--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/15,10,26 ПОКОМ КИ/дв 15,10,26 млрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/15,10,26 ПОКОМ КИ/дв 15,10,26 млрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\10,26\15,10,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BC8D12-6812-4F08-BD1F-D925EF47B93B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C9969D-F0D9-4CA1-BC21-6834AE3349CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="192">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -608,6 +608,9 @@
   <si>
     <t>20,10,</t>
   </si>
+  <si>
+    <t>20,10,ОТМЕНА</t>
+  </si>
 </sst>
 </file>
 
@@ -662,7 +665,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -709,6 +712,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -745,7 +754,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -766,6 +775,11 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -7129,7 +7143,8 @@
     <col min="10" max="10" width="1" customWidth="1"/>
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.28515625" customWidth="1"/>
-    <col min="15" max="23" width="7" customWidth="1"/>
+    <col min="15" max="22" width="7" customWidth="1"/>
+    <col min="23" max="23" width="14" style="24" customWidth="1"/>
     <col min="24" max="25" width="7" style="18" customWidth="1"/>
     <col min="26" max="27" width="5" customWidth="1"/>
     <col min="28" max="37" width="6" customWidth="1"/>
@@ -7163,7 +7178,7 @@
         <v>-0.85</v>
       </c>
       <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
+      <c r="W1" s="20"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
@@ -7220,7 +7235,7 @@
         <v>186</v>
       </c>
       <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
+      <c r="W2" s="21"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -7319,7 +7334,7 @@
       <c r="V3" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="22" t="s">
         <v>187</v>
       </c>
       <c r="X3" s="3" t="s">
@@ -7422,8 +7437,8 @@
       <c r="V4" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="W4" s="1" t="s">
-        <v>190</v>
+      <c r="W4" s="21" t="s">
+        <v>191</v>
       </c>
       <c r="X4" s="1" t="s">
         <v>184</v>
@@ -7547,7 +7562,7 @@
         <f t="shared" si="0"/>
         <v>9671.9104695999995</v>
       </c>
-      <c r="W5" s="4">
+      <c r="W5" s="21">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
@@ -7686,7 +7701,7 @@
         <f>U6-W6</f>
         <v>100</v>
       </c>
-      <c r="W6" s="5">
+      <c r="W6" s="23">
         <v>100</v>
       </c>
       <c r="X6" s="17">
@@ -7824,7 +7839,7 @@
         <f t="shared" ref="V7:V70" si="6">U7-W7</f>
         <v>296.42936999999972</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="23">
         <v>250</v>
       </c>
       <c r="X7" s="17"/>
@@ -7869,7 +7884,7 @@
       </c>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1">
-        <f t="shared" ref="AM7:AN70" si="8">ROUND(G7*V7,0)</f>
+        <f t="shared" ref="AM7:AM70" si="8">ROUND(G7*V7,0)</f>
         <v>296</v>
       </c>
       <c r="AN7" s="1">
@@ -7955,7 +7970,7 @@
         <f t="shared" si="6"/>
         <v>220</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8" s="23">
         <v>100</v>
       </c>
       <c r="X8" s="17">
@@ -8091,7 +8106,7 @@
         <f t="shared" si="6"/>
         <v>61.490000000000038</v>
       </c>
-      <c r="W9" s="5"/>
+      <c r="W9" s="23"/>
       <c r="X9" s="17"/>
       <c r="Y9" s="17"/>
       <c r="Z9" s="1">
@@ -8221,7 +8236,7 @@
         <f t="shared" si="6"/>
         <v>324.13600000000019</v>
       </c>
-      <c r="W10" s="5"/>
+      <c r="W10" s="23"/>
       <c r="X10" s="17"/>
       <c r="Y10" s="17"/>
       <c r="Z10" s="1">
@@ -8349,7 +8364,7 @@
         <f t="shared" si="6"/>
         <v>274.35599999999999</v>
       </c>
-      <c r="W11" s="5"/>
+      <c r="W11" s="23"/>
       <c r="X11" s="17"/>
       <c r="Y11" s="17"/>
       <c r="Z11" s="1">
@@ -8462,7 +8477,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="23"/>
       <c r="X12" s="17"/>
       <c r="Y12" s="17"/>
       <c r="Z12" s="1" t="e">
@@ -8584,7 +8599,7 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="W13" s="5"/>
+      <c r="W13" s="23"/>
       <c r="X13" s="17">
         <f>VLOOKUP(A13,[1]Sheet!$A:$V,21,0)</f>
         <v>120</v>
@@ -8714,7 +8729,7 @@
         <f t="shared" si="6"/>
         <v>90</v>
       </c>
-      <c r="W14" s="5"/>
+      <c r="W14" s="23"/>
       <c r="X14" s="17">
         <f>VLOOKUP(A14,[1]Sheet!$A:$V,21,0)</f>
         <v>180</v>
@@ -8847,7 +8862,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W15" s="5"/>
+      <c r="W15" s="23"/>
       <c r="X15" s="17"/>
       <c r="Y15" s="17"/>
       <c r="Z15" s="1">
@@ -8974,7 +8989,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W16" s="5"/>
+      <c r="W16" s="23"/>
       <c r="X16" s="17"/>
       <c r="Y16" s="17"/>
       <c r="Z16" s="1">
@@ -9099,7 +9114,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W17" s="5"/>
+      <c r="W17" s="23"/>
       <c r="X17" s="17"/>
       <c r="Y17" s="17"/>
       <c r="Z17" s="1">
@@ -9224,7 +9239,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W18" s="5"/>
+      <c r="W18" s="23"/>
       <c r="X18" s="17"/>
       <c r="Y18" s="17"/>
       <c r="Z18" s="1">
@@ -9348,7 +9363,7 @@
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="W19" s="5"/>
+      <c r="W19" s="23"/>
       <c r="X19" s="17">
         <f>VLOOKUP(A19,[1]Sheet!$A:$V,21,0)</f>
         <v>50</v>
@@ -9484,7 +9499,7 @@
         <f t="shared" si="6"/>
         <v>51.830577599999984</v>
       </c>
-      <c r="W20" s="5"/>
+      <c r="W20" s="23"/>
       <c r="X20" s="17"/>
       <c r="Y20" s="17"/>
       <c r="Z20" s="1">
@@ -9610,7 +9625,7 @@
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-      <c r="W21" s="5"/>
+      <c r="W21" s="23"/>
       <c r="X21" s="17">
         <f>VLOOKUP(A21,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -9741,7 +9756,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W22" s="5"/>
+      <c r="W22" s="23"/>
       <c r="X22" s="17"/>
       <c r="Y22" s="17"/>
       <c r="Z22" s="1">
@@ -9866,7 +9881,7 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="W23" s="5"/>
+      <c r="W23" s="23"/>
       <c r="X23" s="17">
         <f>VLOOKUP(A23,[1]Sheet!$A:$V,21,0)</f>
         <v>50</v>
@@ -9998,7 +10013,7 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="W24" s="5"/>
+      <c r="W24" s="23"/>
       <c r="X24" s="17">
         <f>VLOOKUP(A24,[1]Sheet!$A:$V,21,0)</f>
         <v>200</v>
@@ -10117,7 +10132,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W25" s="5"/>
+      <c r="W25" s="23"/>
       <c r="X25" s="17"/>
       <c r="Y25" s="17"/>
       <c r="Z25" s="1" t="e">
@@ -10249,7 +10264,7 @@
         <f t="shared" si="6"/>
         <v>82</v>
       </c>
-      <c r="W26" s="5"/>
+      <c r="W26" s="23"/>
       <c r="X26" s="17">
         <f>VLOOKUP(A26,[1]Sheet!$A:$V,21,0)</f>
         <v>82</v>
@@ -10382,7 +10397,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W27" s="5"/>
+      <c r="W27" s="23"/>
       <c r="X27" s="17"/>
       <c r="Y27" s="17"/>
       <c r="Z27" s="1">
@@ -10508,7 +10523,7 @@
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-      <c r="W28" s="5"/>
+      <c r="W28" s="23"/>
       <c r="X28" s="17">
         <f>VLOOKUP(A28,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -10644,7 +10659,7 @@
         <f t="shared" si="6"/>
         <v>176.08395000000002</v>
       </c>
-      <c r="W29" s="5">
+      <c r="W29" s="23">
         <v>100</v>
       </c>
       <c r="X29" s="17"/>
@@ -10771,7 +10786,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W30" s="5"/>
+      <c r="W30" s="23"/>
       <c r="X30" s="17"/>
       <c r="Y30" s="17"/>
       <c r="Z30" s="1">
@@ -10899,7 +10914,7 @@
         <f t="shared" si="6"/>
         <v>15.452600000000004</v>
       </c>
-      <c r="W31" s="5"/>
+      <c r="W31" s="23"/>
       <c r="X31" s="17"/>
       <c r="Y31" s="17"/>
       <c r="Z31" s="1">
@@ -11024,7 +11039,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W32" s="5"/>
+      <c r="W32" s="23"/>
       <c r="X32" s="17"/>
       <c r="Y32" s="17"/>
       <c r="Z32" s="1">
@@ -11144,7 +11159,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W33" s="5"/>
+      <c r="W33" s="23"/>
       <c r="X33" s="17">
         <f>VLOOKUP(A33,[1]Sheet!$A:$V,21,0)</f>
         <v>80</v>
@@ -11277,7 +11292,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W34" s="5"/>
+      <c r="W34" s="23"/>
       <c r="X34" s="17"/>
       <c r="Y34" s="17"/>
       <c r="Z34" s="1">
@@ -11405,7 +11420,7 @@
         <f t="shared" si="6"/>
         <v>99.840000000000046</v>
       </c>
-      <c r="W35" s="5"/>
+      <c r="W35" s="23"/>
       <c r="X35" s="17"/>
       <c r="Y35" s="17"/>
       <c r="Z35" s="1">
@@ -11535,7 +11550,7 @@
         <f t="shared" si="6"/>
         <v>367.18999999999971</v>
       </c>
-      <c r="W36" s="5"/>
+      <c r="W36" s="23"/>
       <c r="X36" s="17"/>
       <c r="Y36" s="17"/>
       <c r="Z36" s="1">
@@ -11660,7 +11675,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W37" s="5"/>
+      <c r="W37" s="23"/>
       <c r="X37" s="17"/>
       <c r="Y37" s="17"/>
       <c r="Z37" s="1">
@@ -11786,7 +11801,7 @@
         <f t="shared" si="6"/>
         <v>64.340800000000002</v>
       </c>
-      <c r="W38" s="5"/>
+      <c r="W38" s="23"/>
       <c r="X38" s="17"/>
       <c r="Y38" s="17"/>
       <c r="Z38" s="1">
@@ -11916,7 +11931,7 @@
         <f t="shared" si="6"/>
         <v>798.18000000000006</v>
       </c>
-      <c r="W39" s="5"/>
+      <c r="W39" s="23"/>
       <c r="X39" s="17"/>
       <c r="Y39" s="17"/>
       <c r="Z39" s="1">
@@ -12041,7 +12056,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W40" s="5"/>
+      <c r="W40" s="23"/>
       <c r="X40" s="17"/>
       <c r="Y40" s="17"/>
       <c r="Z40" s="1">
@@ -12168,7 +12183,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W41" s="5"/>
+      <c r="W41" s="23"/>
       <c r="X41" s="17"/>
       <c r="Y41" s="17"/>
       <c r="Z41" s="1">
@@ -12296,7 +12311,7 @@
         <f t="shared" si="6"/>
         <v>124.37000000000002</v>
       </c>
-      <c r="W42" s="5"/>
+      <c r="W42" s="23"/>
       <c r="X42" s="17"/>
       <c r="Y42" s="17"/>
       <c r="Z42" s="1">
@@ -12421,7 +12436,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W43" s="5"/>
+      <c r="W43" s="23"/>
       <c r="X43" s="17"/>
       <c r="Y43" s="17"/>
       <c r="Z43" s="1">
@@ -12550,7 +12565,7 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="W44" s="5">
+      <c r="W44" s="23">
         <v>100</v>
       </c>
       <c r="X44" s="17">
@@ -12682,7 +12697,7 @@
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-      <c r="W45" s="5"/>
+      <c r="W45" s="23"/>
       <c r="X45" s="17">
         <f>VLOOKUP(A45,[1]Sheet!$A:$V,21,0)</f>
         <v>300</v>
@@ -12814,7 +12829,7 @@
         <f t="shared" si="6"/>
         <v>404.48</v>
       </c>
-      <c r="W46" s="5"/>
+      <c r="W46" s="23"/>
       <c r="X46" s="17"/>
       <c r="Y46" s="17"/>
       <c r="Z46" s="1">
@@ -12939,7 +12954,7 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="W47" s="5"/>
+      <c r="W47" s="23"/>
       <c r="X47" s="17">
         <f>VLOOKUP(A47,[1]Sheet!$A:$V,21,0)</f>
         <v>80</v>
@@ -13069,7 +13084,7 @@
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="W48" s="5"/>
+      <c r="W48" s="23"/>
       <c r="X48" s="17">
         <f>VLOOKUP(A48,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -13195,7 +13210,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W49" s="5"/>
+      <c r="W49" s="23"/>
       <c r="X49" s="17"/>
       <c r="Y49" s="17"/>
       <c r="Z49" s="1" t="e">
@@ -13321,7 +13336,7 @@
         <f t="shared" si="6"/>
         <v>223</v>
       </c>
-      <c r="W50" s="5"/>
+      <c r="W50" s="23"/>
       <c r="X50" s="17"/>
       <c r="Y50" s="17"/>
       <c r="Z50" s="1">
@@ -13447,7 +13462,7 @@
         <f t="shared" si="6"/>
         <v>162.69000000000003</v>
       </c>
-      <c r="W51" s="5"/>
+      <c r="W51" s="23"/>
       <c r="X51" s="17"/>
       <c r="Y51" s="17"/>
       <c r="Z51" s="1">
@@ -13575,7 +13590,7 @@
         <f t="shared" si="6"/>
         <v>176.32</v>
       </c>
-      <c r="W52" s="5"/>
+      <c r="W52" s="23"/>
       <c r="X52" s="17"/>
       <c r="Y52" s="17"/>
       <c r="Z52" s="1">
@@ -13703,7 +13718,7 @@
         <f t="shared" si="6"/>
         <v>206.18999999999997</v>
       </c>
-      <c r="W53" s="5"/>
+      <c r="W53" s="23"/>
       <c r="X53" s="17"/>
       <c r="Y53" s="17"/>
       <c r="Z53" s="1">
@@ -13827,7 +13842,7 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="W54" s="5"/>
+      <c r="W54" s="23"/>
       <c r="X54" s="17">
         <f>VLOOKUP(A54,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -13963,7 +13978,7 @@
         <f t="shared" si="6"/>
         <v>1119.5899999999997</v>
       </c>
-      <c r="W55" s="5"/>
+      <c r="W55" s="23"/>
       <c r="X55" s="17"/>
       <c r="Y55" s="17"/>
       <c r="Z55" s="1">
@@ -14087,7 +14102,7 @@
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-      <c r="W56" s="5"/>
+      <c r="W56" s="23"/>
       <c r="X56" s="17">
         <f>VLOOKUP(A56,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -14219,7 +14234,7 @@
         <f t="shared" si="6"/>
         <v>3.7571999999999974</v>
       </c>
-      <c r="W57" s="5"/>
+      <c r="W57" s="23"/>
       <c r="X57" s="17"/>
       <c r="Y57" s="17"/>
       <c r="Z57" s="1">
@@ -14346,7 +14361,7 @@
         <f t="shared" si="6"/>
         <v>700</v>
       </c>
-      <c r="W58" s="5"/>
+      <c r="W58" s="23"/>
       <c r="X58" s="17">
         <f>VLOOKUP(A58,[1]Sheet!$A:$V,21,0)</f>
         <v>900</v>
@@ -14477,7 +14492,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W59" s="5"/>
+      <c r="W59" s="23"/>
       <c r="X59" s="17"/>
       <c r="Y59" s="17"/>
       <c r="Z59" s="1">
@@ -14605,7 +14620,7 @@
         <f t="shared" si="6"/>
         <v>25.878399999999999</v>
       </c>
-      <c r="W60" s="5"/>
+      <c r="W60" s="23"/>
       <c r="X60" s="17"/>
       <c r="Y60" s="17"/>
       <c r="Z60" s="1">
@@ -14733,7 +14748,7 @@
         <f t="shared" si="6"/>
         <v>73.577639999999946</v>
       </c>
-      <c r="W61" s="5"/>
+      <c r="W61" s="23"/>
       <c r="X61" s="17"/>
       <c r="Y61" s="17"/>
       <c r="Z61" s="1">
@@ -14858,7 +14873,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W62" s="5"/>
+      <c r="W62" s="23"/>
       <c r="X62" s="17"/>
       <c r="Y62" s="17"/>
       <c r="Z62" s="1">
@@ -14990,7 +15005,7 @@
         <f t="shared" si="6"/>
         <v>200.43999999999977</v>
       </c>
-      <c r="W63" s="5"/>
+      <c r="W63" s="23"/>
       <c r="X63" s="17"/>
       <c r="Y63" s="17"/>
       <c r="Z63" s="1">
@@ -15115,7 +15130,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W64" s="5"/>
+      <c r="W64" s="23"/>
       <c r="X64" s="17"/>
       <c r="Y64" s="17"/>
       <c r="Z64" s="1">
@@ -15240,7 +15255,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W65" s="5"/>
+      <c r="W65" s="23"/>
       <c r="X65" s="17"/>
       <c r="Y65" s="17"/>
       <c r="Z65" s="1">
@@ -15362,7 +15377,7 @@
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="W66" s="5"/>
+      <c r="W66" s="23"/>
       <c r="X66" s="17">
         <f>VLOOKUP(A66,[1]Sheet!$A:$V,21,0)</f>
         <v>130</v>
@@ -15494,7 +15509,7 @@
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-      <c r="W67" s="5"/>
+      <c r="W67" s="23"/>
       <c r="X67" s="17">
         <f>VLOOKUP(A67,[1]Sheet!$A:$V,21,0)</f>
         <v>150</v>
@@ -15625,7 +15640,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W68" s="5"/>
+      <c r="W68" s="23"/>
       <c r="X68" s="17"/>
       <c r="Y68" s="17"/>
       <c r="Z68" s="1">
@@ -15750,7 +15765,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W69" s="5"/>
+      <c r="W69" s="23"/>
       <c r="X69" s="17"/>
       <c r="Y69" s="17"/>
       <c r="Z69" s="1">
@@ -15873,7 +15888,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="W70" s="5"/>
+      <c r="W70" s="23"/>
       <c r="X70" s="17"/>
       <c r="Y70" s="17"/>
       <c r="Z70" s="1">
@@ -16000,7 +16015,7 @@
         <f t="shared" ref="V71:V131" si="23">U71-W71</f>
         <v>0</v>
       </c>
-      <c r="W71" s="5"/>
+      <c r="W71" s="23"/>
       <c r="X71" s="17"/>
       <c r="Y71" s="17"/>
       <c r="Z71" s="1">
@@ -16043,7 +16058,7 @@
       </c>
       <c r="AL71" s="1"/>
       <c r="AM71" s="1">
-        <f t="shared" ref="AM71:AN131" si="25">ROUND(G71*V71,0)</f>
+        <f t="shared" ref="AM71:AM131" si="25">ROUND(G71*V71,0)</f>
         <v>0</v>
       </c>
       <c r="AN71" s="1">
@@ -16128,7 +16143,7 @@
         <f t="shared" si="23"/>
         <v>32.200000000000017</v>
       </c>
-      <c r="W72" s="5"/>
+      <c r="W72" s="23"/>
       <c r="X72" s="17"/>
       <c r="Y72" s="17"/>
       <c r="Z72" s="1">
@@ -16256,7 +16271,7 @@
         <f t="shared" si="23"/>
         <v>29.219999999999914</v>
       </c>
-      <c r="W73" s="5"/>
+      <c r="W73" s="23"/>
       <c r="X73" s="17"/>
       <c r="Y73" s="17"/>
       <c r="Z73" s="1">
@@ -16386,7 +16401,7 @@
         <f t="shared" si="23"/>
         <v>16.339999999999947</v>
       </c>
-      <c r="W74" s="5"/>
+      <c r="W74" s="23"/>
       <c r="X74" s="17"/>
       <c r="Y74" s="17"/>
       <c r="Z74" s="1">
@@ -16503,7 +16518,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W75" s="5"/>
+      <c r="W75" s="23"/>
       <c r="X75" s="17"/>
       <c r="Y75" s="17"/>
       <c r="Z75" s="1" t="e">
@@ -16626,7 +16641,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W76" s="5"/>
+      <c r="W76" s="23"/>
       <c r="X76" s="17"/>
       <c r="Y76" s="17"/>
       <c r="Z76" s="1">
@@ -16751,7 +16766,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W77" s="5"/>
+      <c r="W77" s="23"/>
       <c r="X77" s="17"/>
       <c r="Y77" s="17"/>
       <c r="Z77" s="1">
@@ -16872,7 +16887,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W78" s="5"/>
+      <c r="W78" s="23"/>
       <c r="X78" s="17"/>
       <c r="Y78" s="17"/>
       <c r="Z78" s="1">
@@ -16997,7 +17012,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W79" s="5"/>
+      <c r="W79" s="23"/>
       <c r="X79" s="17"/>
       <c r="Y79" s="17"/>
       <c r="Z79" s="1">
@@ -17125,7 +17140,7 @@
         <f t="shared" si="23"/>
         <v>10.599999999999994</v>
       </c>
-      <c r="W80" s="5"/>
+      <c r="W80" s="23"/>
       <c r="X80" s="17"/>
       <c r="Y80" s="17"/>
       <c r="Z80" s="1">
@@ -17238,7 +17253,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W81" s="5"/>
+      <c r="W81" s="23"/>
       <c r="X81" s="17"/>
       <c r="Y81" s="17"/>
       <c r="Z81" s="1" t="e">
@@ -17353,7 +17368,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W82" s="5"/>
+      <c r="W82" s="23"/>
       <c r="X82" s="17"/>
       <c r="Y82" s="17"/>
       <c r="Z82" s="1" t="e">
@@ -17480,7 +17495,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W83" s="5"/>
+      <c r="W83" s="23"/>
       <c r="X83" s="17"/>
       <c r="Y83" s="17"/>
       <c r="Z83" s="1">
@@ -17612,7 +17627,7 @@
         <f t="shared" si="23"/>
         <v>172.73820000000006</v>
       </c>
-      <c r="W84" s="5"/>
+      <c r="W84" s="23"/>
       <c r="X84" s="17"/>
       <c r="Y84" s="17"/>
       <c r="Z84" s="1">
@@ -17725,7 +17740,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W85" s="5"/>
+      <c r="W85" s="23"/>
       <c r="X85" s="17"/>
       <c r="Y85" s="17"/>
       <c r="Z85" s="1" t="e">
@@ -17857,7 +17872,7 @@
         <f t="shared" si="23"/>
         <v>267.97099999999983</v>
       </c>
-      <c r="W86" s="5">
+      <c r="W86" s="23">
         <v>100</v>
       </c>
       <c r="X86" s="17"/>
@@ -17987,7 +18002,7 @@
         <f t="shared" si="23"/>
         <v>19.167066000001114</v>
       </c>
-      <c r="W87" s="5"/>
+      <c r="W87" s="23"/>
       <c r="X87" s="17"/>
       <c r="Y87" s="17"/>
       <c r="Z87" s="1">
@@ -18117,7 +18132,7 @@
         <f t="shared" si="23"/>
         <v>302.75659999999993</v>
       </c>
-      <c r="W88" s="5">
+      <c r="W88" s="23">
         <v>250</v>
       </c>
       <c r="X88" s="17"/>
@@ -18232,7 +18247,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W89" s="5"/>
+      <c r="W89" s="23"/>
       <c r="X89" s="17"/>
       <c r="Y89" s="17"/>
       <c r="Z89" s="1" t="e">
@@ -18356,7 +18371,7 @@
         <f t="shared" si="23"/>
         <v>80</v>
       </c>
-      <c r="W90" s="5"/>
+      <c r="W90" s="23"/>
       <c r="X90" s="17">
         <f>VLOOKUP(A90,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -18482,7 +18497,7 @@
         <f t="shared" si="23"/>
         <v>20</v>
       </c>
-      <c r="W91" s="5"/>
+      <c r="W91" s="23"/>
       <c r="X91" s="17">
         <f>VLOOKUP(A91,[1]Sheet!$A:$V,21,0)</f>
         <v>30</v>
@@ -18610,7 +18625,7 @@
         <f t="shared" si="23"/>
         <v>60</v>
       </c>
-      <c r="W92" s="5"/>
+      <c r="W92" s="23"/>
       <c r="X92" s="17">
         <f>VLOOKUP(A92,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -18733,7 +18748,7 @@
         <f t="shared" si="23"/>
         <v>40</v>
       </c>
-      <c r="W93" s="5"/>
+      <c r="W93" s="23"/>
       <c r="X93" s="17">
         <f>VLOOKUP(A93,[1]Sheet!$A:$V,21,0)</f>
         <v>40</v>
@@ -18863,7 +18878,7 @@
         <f t="shared" si="23"/>
         <v>60</v>
       </c>
-      <c r="W94" s="5"/>
+      <c r="W94" s="23"/>
       <c r="X94" s="17">
         <f>VLOOKUP(A94,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -18991,7 +19006,7 @@
         <f t="shared" si="23"/>
         <v>20</v>
       </c>
-      <c r="W95" s="5"/>
+      <c r="W95" s="23"/>
       <c r="X95" s="17">
         <f>VLOOKUP(A95,[1]Sheet!$A:$V,21,0)</f>
         <v>40</v>
@@ -19118,7 +19133,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W96" s="5"/>
+      <c r="W96" s="23"/>
       <c r="X96" s="17"/>
       <c r="Y96" s="17"/>
       <c r="Z96" s="1">
@@ -19233,7 +19248,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W97" s="5"/>
+      <c r="W97" s="23"/>
       <c r="X97" s="17"/>
       <c r="Y97" s="17"/>
       <c r="Z97" s="1" t="e">
@@ -19361,7 +19376,7 @@
         <f t="shared" si="23"/>
         <v>100</v>
       </c>
-      <c r="W98" s="5"/>
+      <c r="W98" s="23"/>
       <c r="X98" s="17">
         <f>VLOOKUP(A98,[1]Sheet!$A:$V,21,0)</f>
         <v>150</v>
@@ -19491,7 +19506,7 @@
         <f t="shared" si="23"/>
         <v>80</v>
       </c>
-      <c r="W99" s="5"/>
+      <c r="W99" s="23"/>
       <c r="X99" s="17">
         <f>VLOOKUP(A99,[1]Sheet!$A:$V,21,0)</f>
         <v>200</v>
@@ -19610,7 +19625,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W100" s="5"/>
+      <c r="W100" s="23"/>
       <c r="X100" s="17"/>
       <c r="Y100" s="17"/>
       <c r="Z100" s="1" t="e">
@@ -19738,7 +19753,7 @@
         <f t="shared" si="23"/>
         <v>80</v>
       </c>
-      <c r="W101" s="5"/>
+      <c r="W101" s="23"/>
       <c r="X101" s="17">
         <f>VLOOKUP(A101,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -19868,7 +19883,7 @@
         <f t="shared" si="23"/>
         <v>30</v>
       </c>
-      <c r="W102" s="5"/>
+      <c r="W102" s="23"/>
       <c r="X102" s="17">
         <f>VLOOKUP(A102,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -19998,7 +20013,7 @@
         <f t="shared" si="23"/>
         <v>20</v>
       </c>
-      <c r="W103" s="5"/>
+      <c r="W103" s="23"/>
       <c r="X103" s="17">
         <f>VLOOKUP(A103,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -20117,7 +20132,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W104" s="5"/>
+      <c r="W104" s="23"/>
       <c r="X104" s="17"/>
       <c r="Y104" s="17"/>
       <c r="Z104" s="1" t="e">
@@ -20248,7 +20263,7 @@
         <f t="shared" si="23"/>
         <v>200</v>
       </c>
-      <c r="W105" s="5"/>
+      <c r="W105" s="23"/>
       <c r="X105" s="17">
         <f>VLOOKUP(A105,[1]Sheet!$A:$V,21,0)</f>
         <v>250</v>
@@ -20378,7 +20393,7 @@
         <f t="shared" si="23"/>
         <v>80</v>
       </c>
-      <c r="W106" s="5"/>
+      <c r="W106" s="23"/>
       <c r="X106" s="17">
         <f>VLOOKUP(A106,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -20508,7 +20523,7 @@
         <f t="shared" si="23"/>
         <v>50</v>
       </c>
-      <c r="W107" s="5"/>
+      <c r="W107" s="23"/>
       <c r="X107" s="17">
         <f>VLOOKUP(A107,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -20627,7 +20642,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W108" s="5"/>
+      <c r="W108" s="23"/>
       <c r="X108" s="17"/>
       <c r="Y108" s="17"/>
       <c r="Z108" s="1" t="e">
@@ -20752,7 +20767,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W109" s="5"/>
+      <c r="W109" s="23"/>
       <c r="X109" s="17"/>
       <c r="Y109" s="17"/>
       <c r="Z109" s="1">
@@ -20877,7 +20892,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W110" s="5"/>
+      <c r="W110" s="23"/>
       <c r="X110" s="17"/>
       <c r="Y110" s="17"/>
       <c r="Z110" s="1">
@@ -21002,7 +21017,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W111" s="5"/>
+      <c r="W111" s="23"/>
       <c r="X111" s="17"/>
       <c r="Y111" s="17"/>
       <c r="Z111" s="1">
@@ -21115,7 +21130,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W112" s="5"/>
+      <c r="W112" s="23"/>
       <c r="X112" s="17"/>
       <c r="Y112" s="17"/>
       <c r="Z112" s="1" t="e">
@@ -21246,7 +21261,7 @@
         <f t="shared" si="23"/>
         <v>120</v>
       </c>
-      <c r="W113" s="5"/>
+      <c r="W113" s="23"/>
       <c r="X113" s="17">
         <f>VLOOKUP(A113,[1]Sheet!$A:$V,21,0)</f>
         <v>150</v>
@@ -21380,7 +21395,7 @@
         <f t="shared" si="23"/>
         <v>80</v>
       </c>
-      <c r="W114" s="5"/>
+      <c r="W114" s="23"/>
       <c r="X114" s="17">
         <f>VLOOKUP(A114,[1]Sheet!$A:$V,21,0)</f>
         <v>100</v>
@@ -21514,7 +21529,7 @@
         <f t="shared" si="23"/>
         <v>29.29506599999997</v>
       </c>
-      <c r="W115" s="5"/>
+      <c r="W115" s="23"/>
       <c r="X115" s="17"/>
       <c r="Y115" s="17"/>
       <c r="Z115" s="1">
@@ -21641,7 +21656,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W116" s="5"/>
+      <c r="W116" s="23"/>
       <c r="X116" s="17"/>
       <c r="Y116" s="17"/>
       <c r="Z116" s="1">
@@ -21764,7 +21779,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W117" s="5"/>
+      <c r="W117" s="23"/>
       <c r="X117" s="17"/>
       <c r="Y117" s="17"/>
       <c r="Z117" s="1">
@@ -21890,7 +21905,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W118" s="5"/>
+      <c r="W118" s="23"/>
       <c r="X118" s="17"/>
       <c r="Y118" s="17"/>
       <c r="Z118" s="1">
@@ -22015,7 +22030,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W119" s="5"/>
+      <c r="W119" s="23"/>
       <c r="X119" s="17"/>
       <c r="Y119" s="17"/>
       <c r="Z119" s="1">
@@ -22132,7 +22147,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W120" s="5"/>
+      <c r="W120" s="23"/>
       <c r="X120" s="17"/>
       <c r="Y120" s="17"/>
       <c r="Z120" s="1">
@@ -22245,7 +22260,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W121" s="5"/>
+      <c r="W121" s="23"/>
       <c r="X121" s="17"/>
       <c r="Y121" s="17"/>
       <c r="Z121" s="1" t="e">
@@ -22367,7 +22382,7 @@
         <f t="shared" si="23"/>
         <v>80</v>
       </c>
-      <c r="W122" s="5"/>
+      <c r="W122" s="23"/>
       <c r="X122" s="17">
         <f>VLOOKUP(A122,[1]Sheet!$A:$V,21,0)</f>
         <v>150</v>
@@ -22495,7 +22510,7 @@
         <f t="shared" si="23"/>
         <v>50</v>
       </c>
-      <c r="W123" s="5"/>
+      <c r="W123" s="23"/>
       <c r="X123" s="17">
         <f>VLOOKUP(A123,[1]Sheet!$A:$V,21,0)</f>
         <v>150</v>
@@ -22628,7 +22643,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W124" s="5"/>
+      <c r="W124" s="23"/>
       <c r="X124" s="17"/>
       <c r="Y124" s="17"/>
       <c r="Z124" s="1">
@@ -22750,7 +22765,7 @@
         <f t="shared" si="23"/>
         <v>80</v>
       </c>
-      <c r="W125" s="5"/>
+      <c r="W125" s="23"/>
       <c r="X125" s="17">
         <f>VLOOKUP(A125,[1]Sheet!$A:$V,21,0)</f>
         <v>150</v>
@@ -22881,7 +22896,7 @@
         <f t="shared" si="23"/>
         <v>40</v>
       </c>
-      <c r="W126" s="5"/>
+      <c r="W126" s="23"/>
       <c r="X126" s="17">
         <f>VLOOKUP(A126,[1]Sheet!$A:$V,21,0)</f>
         <v>50</v>
@@ -23010,7 +23025,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W127" s="5"/>
+      <c r="W127" s="23"/>
       <c r="X127" s="17"/>
       <c r="Y127" s="17"/>
       <c r="Z127" s="1">
@@ -23129,7 +23144,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W128" s="5"/>
+      <c r="W128" s="23"/>
       <c r="X128" s="17"/>
       <c r="Y128" s="17"/>
       <c r="Z128" s="1" t="e">
@@ -23238,7 +23253,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W129" s="5"/>
+      <c r="W129" s="23"/>
       <c r="X129" s="17"/>
       <c r="Y129" s="17"/>
       <c r="Z129" s="1" t="e">
@@ -23349,7 +23364,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W130" s="5"/>
+      <c r="W130" s="23"/>
       <c r="X130" s="17"/>
       <c r="Y130" s="17"/>
       <c r="Z130" s="1" t="e">
@@ -23460,7 +23475,7 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W131" s="5"/>
+      <c r="W131" s="23"/>
       <c r="X131" s="17"/>
       <c r="Y131" s="17"/>
       <c r="Z131" s="1" t="e">
@@ -23549,7 +23564,7 @@
       <c r="T132" s="1"/>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
-      <c r="W132" s="1"/>
+      <c r="W132" s="21"/>
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
@@ -23604,7 +23619,7 @@
       <c r="T133" s="1"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
-      <c r="W133" s="1"/>
+      <c r="W133" s="21"/>
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
@@ -23659,7 +23674,7 @@
       <c r="T134" s="1"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
-      <c r="W134" s="1"/>
+      <c r="W134" s="21"/>
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
@@ -23714,7 +23729,7 @@
       <c r="T135" s="1"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
-      <c r="W135" s="1"/>
+      <c r="W135" s="21"/>
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
@@ -23769,7 +23784,7 @@
       <c r="T136" s="1"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
-      <c r="W136" s="1"/>
+      <c r="W136" s="21"/>
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
@@ -23824,7 +23839,7 @@
       <c r="T137" s="1"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
-      <c r="W137" s="1"/>
+      <c r="W137" s="21"/>
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
@@ -23879,7 +23894,7 @@
       <c r="T138" s="1"/>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
-      <c r="W138" s="1"/>
+      <c r="W138" s="21"/>
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
@@ -23934,7 +23949,7 @@
       <c r="T139" s="1"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
-      <c r="W139" s="1"/>
+      <c r="W139" s="21"/>
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
@@ -23989,7 +24004,7 @@
       <c r="T140" s="1"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
-      <c r="W140" s="1"/>
+      <c r="W140" s="21"/>
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
@@ -24044,7 +24059,7 @@
       <c r="T141" s="1"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
-      <c r="W141" s="1"/>
+      <c r="W141" s="21"/>
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
@@ -24099,7 +24114,7 @@
       <c r="T142" s="1"/>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
-      <c r="W142" s="1"/>
+      <c r="W142" s="21"/>
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
@@ -24154,7 +24169,7 @@
       <c r="T143" s="1"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
-      <c r="W143" s="1"/>
+      <c r="W143" s="21"/>
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
@@ -24209,7 +24224,7 @@
       <c r="T144" s="1"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
-      <c r="W144" s="1"/>
+      <c r="W144" s="21"/>
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
@@ -24264,7 +24279,7 @@
       <c r="T145" s="1"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
-      <c r="W145" s="1"/>
+      <c r="W145" s="21"/>
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
@@ -24319,7 +24334,7 @@
       <c r="T146" s="1"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
-      <c r="W146" s="1"/>
+      <c r="W146" s="21"/>
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
@@ -24374,7 +24389,7 @@
       <c r="T147" s="1"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
-      <c r="W147" s="1"/>
+      <c r="W147" s="21"/>
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
@@ -24429,7 +24444,7 @@
       <c r="T148" s="1"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
-      <c r="W148" s="1"/>
+      <c r="W148" s="21"/>
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
@@ -24484,7 +24499,7 @@
       <c r="T149" s="1"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
-      <c r="W149" s="1"/>
+      <c r="W149" s="21"/>
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
@@ -24539,7 +24554,7 @@
       <c r="T150" s="1"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
-      <c r="W150" s="1"/>
+      <c r="W150" s="21"/>
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
@@ -24594,7 +24609,7 @@
       <c r="T151" s="1"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
-      <c r="W151" s="1"/>
+      <c r="W151" s="21"/>
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
@@ -24649,7 +24664,7 @@
       <c r="T152" s="1"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
-      <c r="W152" s="1"/>
+      <c r="W152" s="21"/>
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
@@ -24704,7 +24719,7 @@
       <c r="T153" s="1"/>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
-      <c r="W153" s="1"/>
+      <c r="W153" s="21"/>
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
@@ -24759,7 +24774,7 @@
       <c r="T154" s="1"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
-      <c r="W154" s="1"/>
+      <c r="W154" s="21"/>
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
@@ -24814,7 +24829,7 @@
       <c r="T155" s="1"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
-      <c r="W155" s="1"/>
+      <c r="W155" s="21"/>
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
@@ -24869,7 +24884,7 @@
       <c r="T156" s="1"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
-      <c r="W156" s="1"/>
+      <c r="W156" s="21"/>
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
@@ -24924,7 +24939,7 @@
       <c r="T157" s="1"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
-      <c r="W157" s="1"/>
+      <c r="W157" s="21"/>
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
@@ -24979,7 +24994,7 @@
       <c r="T158" s="1"/>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
-      <c r="W158" s="1"/>
+      <c r="W158" s="21"/>
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
@@ -25034,7 +25049,7 @@
       <c r="T159" s="1"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
-      <c r="W159" s="1"/>
+      <c r="W159" s="21"/>
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
@@ -25089,7 +25104,7 @@
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
-      <c r="W160" s="1"/>
+      <c r="W160" s="21"/>
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
@@ -25144,7 +25159,7 @@
       <c r="T161" s="1"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
-      <c r="W161" s="1"/>
+      <c r="W161" s="21"/>
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
@@ -25199,7 +25214,7 @@
       <c r="T162" s="1"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
-      <c r="W162" s="1"/>
+      <c r="W162" s="21"/>
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
@@ -25254,7 +25269,7 @@
       <c r="T163" s="1"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
-      <c r="W163" s="1"/>
+      <c r="W163" s="21"/>
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
@@ -25309,7 +25324,7 @@
       <c r="T164" s="1"/>
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
-      <c r="W164" s="1"/>
+      <c r="W164" s="21"/>
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
@@ -25364,7 +25379,7 @@
       <c r="T165" s="1"/>
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
-      <c r="W165" s="1"/>
+      <c r="W165" s="21"/>
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
@@ -25419,7 +25434,7 @@
       <c r="T166" s="1"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
-      <c r="W166" s="1"/>
+      <c r="W166" s="21"/>
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
@@ -25474,7 +25489,7 @@
       <c r="T167" s="1"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
-      <c r="W167" s="1"/>
+      <c r="W167" s="21"/>
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
@@ -25529,7 +25544,7 @@
       <c r="T168" s="1"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
-      <c r="W168" s="1"/>
+      <c r="W168" s="21"/>
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
@@ -25584,7 +25599,7 @@
       <c r="T169" s="1"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
-      <c r="W169" s="1"/>
+      <c r="W169" s="21"/>
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
@@ -25639,7 +25654,7 @@
       <c r="T170" s="1"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
-      <c r="W170" s="1"/>
+      <c r="W170" s="21"/>
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
@@ -25694,7 +25709,7 @@
       <c r="T171" s="1"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
-      <c r="W171" s="1"/>
+      <c r="W171" s="21"/>
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
@@ -25749,7 +25764,7 @@
       <c r="T172" s="1"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
-      <c r="W172" s="1"/>
+      <c r="W172" s="21"/>
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
@@ -25804,7 +25819,7 @@
       <c r="T173" s="1"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
-      <c r="W173" s="1"/>
+      <c r="W173" s="21"/>
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
@@ -25859,7 +25874,7 @@
       <c r="T174" s="1"/>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
-      <c r="W174" s="1"/>
+      <c r="W174" s="21"/>
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
@@ -25914,7 +25929,7 @@
       <c r="T175" s="1"/>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
-      <c r="W175" s="1"/>
+      <c r="W175" s="21"/>
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
@@ -25969,7 +25984,7 @@
       <c r="T176" s="1"/>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
-      <c r="W176" s="1"/>
+      <c r="W176" s="21"/>
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
@@ -26024,7 +26039,7 @@
       <c r="T177" s="1"/>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
-      <c r="W177" s="1"/>
+      <c r="W177" s="21"/>
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
@@ -26079,7 +26094,7 @@
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
-      <c r="W178" s="1"/>
+      <c r="W178" s="21"/>
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
@@ -26134,7 +26149,7 @@
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
-      <c r="W179" s="1"/>
+      <c r="W179" s="21"/>
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
@@ -26189,7 +26204,7 @@
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
-      <c r="W180" s="1"/>
+      <c r="W180" s="21"/>
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
@@ -26244,7 +26259,7 @@
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
-      <c r="W181" s="1"/>
+      <c r="W181" s="21"/>
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
@@ -26299,7 +26314,7 @@
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
-      <c r="W182" s="1"/>
+      <c r="W182" s="21"/>
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
@@ -26354,7 +26369,7 @@
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
-      <c r="W183" s="1"/>
+      <c r="W183" s="21"/>
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
@@ -26409,7 +26424,7 @@
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
-      <c r="W184" s="1"/>
+      <c r="W184" s="21"/>
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
@@ -26464,7 +26479,7 @@
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
-      <c r="W185" s="1"/>
+      <c r="W185" s="21"/>
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
@@ -26519,7 +26534,7 @@
       <c r="T186" s="1"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
-      <c r="W186" s="1"/>
+      <c r="W186" s="21"/>
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
@@ -26574,7 +26589,7 @@
       <c r="T187" s="1"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
-      <c r="W187" s="1"/>
+      <c r="W187" s="21"/>
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
@@ -26629,7 +26644,7 @@
       <c r="T188" s="1"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
-      <c r="W188" s="1"/>
+      <c r="W188" s="21"/>
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
@@ -26684,7 +26699,7 @@
       <c r="T189" s="1"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
-      <c r="W189" s="1"/>
+      <c r="W189" s="21"/>
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
@@ -26739,7 +26754,7 @@
       <c r="T190" s="1"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
-      <c r="W190" s="1"/>
+      <c r="W190" s="21"/>
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
@@ -26794,7 +26809,7 @@
       <c r="T191" s="1"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
-      <c r="W191" s="1"/>
+      <c r="W191" s="21"/>
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
@@ -26849,7 +26864,7 @@
       <c r="T192" s="1"/>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
-      <c r="W192" s="1"/>
+      <c r="W192" s="21"/>
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
@@ -26904,7 +26919,7 @@
       <c r="T193" s="1"/>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
-      <c r="W193" s="1"/>
+      <c r="W193" s="21"/>
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
@@ -26959,7 +26974,7 @@
       <c r="T194" s="1"/>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
-      <c r="W194" s="1"/>
+      <c r="W194" s="21"/>
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
@@ -27014,7 +27029,7 @@
       <c r="T195" s="1"/>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
-      <c r="W195" s="1"/>
+      <c r="W195" s="21"/>
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
@@ -27069,7 +27084,7 @@
       <c r="T196" s="1"/>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
-      <c r="W196" s="1"/>
+      <c r="W196" s="21"/>
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
@@ -27124,7 +27139,7 @@
       <c r="T197" s="1"/>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
-      <c r="W197" s="1"/>
+      <c r="W197" s="21"/>
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
@@ -27179,7 +27194,7 @@
       <c r="T198" s="1"/>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
-      <c r="W198" s="1"/>
+      <c r="W198" s="21"/>
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
@@ -27234,7 +27249,7 @@
       <c r="T199" s="1"/>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
-      <c r="W199" s="1"/>
+      <c r="W199" s="21"/>
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
@@ -27289,7 +27304,7 @@
       <c r="T200" s="1"/>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
-      <c r="W200" s="1"/>
+      <c r="W200" s="21"/>
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
@@ -27344,7 +27359,7 @@
       <c r="T201" s="1"/>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
-      <c r="W201" s="1"/>
+      <c r="W201" s="21"/>
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
@@ -27399,7 +27414,7 @@
       <c r="T202" s="1"/>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
-      <c r="W202" s="1"/>
+      <c r="W202" s="21"/>
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
@@ -27454,7 +27469,7 @@
       <c r="T203" s="1"/>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
-      <c r="W203" s="1"/>
+      <c r="W203" s="21"/>
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
@@ -27509,7 +27524,7 @@
       <c r="T204" s="1"/>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
-      <c r="W204" s="1"/>
+      <c r="W204" s="21"/>
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
@@ -27564,7 +27579,7 @@
       <c r="T205" s="1"/>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
-      <c r="W205" s="1"/>
+      <c r="W205" s="21"/>
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
@@ -27619,7 +27634,7 @@
       <c r="T206" s="1"/>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
-      <c r="W206" s="1"/>
+      <c r="W206" s="21"/>
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
@@ -27674,7 +27689,7 @@
       <c r="T207" s="1"/>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
-      <c r="W207" s="1"/>
+      <c r="W207" s="21"/>
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
@@ -27729,7 +27744,7 @@
       <c r="T208" s="1"/>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
-      <c r="W208" s="1"/>
+      <c r="W208" s="21"/>
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
@@ -27784,7 +27799,7 @@
       <c r="T209" s="1"/>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
-      <c r="W209" s="1"/>
+      <c r="W209" s="21"/>
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
@@ -27839,7 +27854,7 @@
       <c r="T210" s="1"/>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
-      <c r="W210" s="1"/>
+      <c r="W210" s="21"/>
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
@@ -27894,7 +27909,7 @@
       <c r="T211" s="1"/>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
-      <c r="W211" s="1"/>
+      <c r="W211" s="21"/>
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
@@ -27949,7 +27964,7 @@
       <c r="T212" s="1"/>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
-      <c r="W212" s="1"/>
+      <c r="W212" s="21"/>
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
@@ -28004,7 +28019,7 @@
       <c r="T213" s="1"/>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
-      <c r="W213" s="1"/>
+      <c r="W213" s="21"/>
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
@@ -28059,7 +28074,7 @@
       <c r="T214" s="1"/>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
-      <c r="W214" s="1"/>
+      <c r="W214" s="21"/>
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
@@ -28114,7 +28129,7 @@
       <c r="T215" s="1"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
-      <c r="W215" s="1"/>
+      <c r="W215" s="21"/>
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
@@ -28169,7 +28184,7 @@
       <c r="T216" s="1"/>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
-      <c r="W216" s="1"/>
+      <c r="W216" s="21"/>
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
@@ -28224,7 +28239,7 @@
       <c r="T217" s="1"/>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
-      <c r="W217" s="1"/>
+      <c r="W217" s="21"/>
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
@@ -28279,7 +28294,7 @@
       <c r="T218" s="1"/>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
-      <c r="W218" s="1"/>
+      <c r="W218" s="21"/>
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
@@ -28334,7 +28349,7 @@
       <c r="T219" s="1"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
-      <c r="W219" s="1"/>
+      <c r="W219" s="21"/>
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
@@ -28389,7 +28404,7 @@
       <c r="T220" s="1"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
-      <c r="W220" s="1"/>
+      <c r="W220" s="21"/>
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
@@ -28444,7 +28459,7 @@
       <c r="T221" s="1"/>
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
-      <c r="W221" s="1"/>
+      <c r="W221" s="21"/>
       <c r="X221" s="1"/>
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
@@ -28499,7 +28514,7 @@
       <c r="T222" s="1"/>
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
-      <c r="W222" s="1"/>
+      <c r="W222" s="21"/>
       <c r="X222" s="1"/>
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
@@ -28554,7 +28569,7 @@
       <c r="T223" s="1"/>
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
-      <c r="W223" s="1"/>
+      <c r="W223" s="21"/>
       <c r="X223" s="1"/>
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
@@ -28609,7 +28624,7 @@
       <c r="T224" s="1"/>
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
-      <c r="W224" s="1"/>
+      <c r="W224" s="21"/>
       <c r="X224" s="1"/>
       <c r="Y224" s="1"/>
       <c r="Z224" s="1"/>
@@ -28664,7 +28679,7 @@
       <c r="T225" s="1"/>
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
-      <c r="W225" s="1"/>
+      <c r="W225" s="21"/>
       <c r="X225" s="1"/>
       <c r="Y225" s="1"/>
       <c r="Z225" s="1"/>
@@ -28719,7 +28734,7 @@
       <c r="T226" s="1"/>
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
-      <c r="W226" s="1"/>
+      <c r="W226" s="21"/>
       <c r="X226" s="1"/>
       <c r="Y226" s="1"/>
       <c r="Z226" s="1"/>
@@ -28774,7 +28789,7 @@
       <c r="T227" s="1"/>
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
-      <c r="W227" s="1"/>
+      <c r="W227" s="21"/>
       <c r="X227" s="1"/>
       <c r="Y227" s="1"/>
       <c r="Z227" s="1"/>
@@ -28829,7 +28844,7 @@
       <c r="T228" s="1"/>
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
-      <c r="W228" s="1"/>
+      <c r="W228" s="21"/>
       <c r="X228" s="1"/>
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
@@ -28884,7 +28899,7 @@
       <c r="T229" s="1"/>
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
-      <c r="W229" s="1"/>
+      <c r="W229" s="21"/>
       <c r="X229" s="1"/>
       <c r="Y229" s="1"/>
       <c r="Z229" s="1"/>
@@ -28939,7 +28954,7 @@
       <c r="T230" s="1"/>
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
-      <c r="W230" s="1"/>
+      <c r="W230" s="21"/>
       <c r="X230" s="1"/>
       <c r="Y230" s="1"/>
       <c r="Z230" s="1"/>
@@ -28994,7 +29009,7 @@
       <c r="T231" s="1"/>
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
-      <c r="W231" s="1"/>
+      <c r="W231" s="21"/>
       <c r="X231" s="1"/>
       <c r="Y231" s="1"/>
       <c r="Z231" s="1"/>
@@ -29049,7 +29064,7 @@
       <c r="T232" s="1"/>
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
-      <c r="W232" s="1"/>
+      <c r="W232" s="21"/>
       <c r="X232" s="1"/>
       <c r="Y232" s="1"/>
       <c r="Z232" s="1"/>
@@ -29104,7 +29119,7 @@
       <c r="T233" s="1"/>
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
-      <c r="W233" s="1"/>
+      <c r="W233" s="21"/>
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
       <c r="Z233" s="1"/>
@@ -29159,7 +29174,7 @@
       <c r="T234" s="1"/>
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
-      <c r="W234" s="1"/>
+      <c r="W234" s="21"/>
       <c r="X234" s="1"/>
       <c r="Y234" s="1"/>
       <c r="Z234" s="1"/>
@@ -29214,7 +29229,7 @@
       <c r="T235" s="1"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
-      <c r="W235" s="1"/>
+      <c r="W235" s="21"/>
       <c r="X235" s="1"/>
       <c r="Y235" s="1"/>
       <c r="Z235" s="1"/>
@@ -29269,7 +29284,7 @@
       <c r="T236" s="1"/>
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
-      <c r="W236" s="1"/>
+      <c r="W236" s="21"/>
       <c r="X236" s="1"/>
       <c r="Y236" s="1"/>
       <c r="Z236" s="1"/>
@@ -29324,7 +29339,7 @@
       <c r="T237" s="1"/>
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
-      <c r="W237" s="1"/>
+      <c r="W237" s="21"/>
       <c r="X237" s="1"/>
       <c r="Y237" s="1"/>
       <c r="Z237" s="1"/>
@@ -29379,7 +29394,7 @@
       <c r="T238" s="1"/>
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
-      <c r="W238" s="1"/>
+      <c r="W238" s="21"/>
       <c r="X238" s="1"/>
       <c r="Y238" s="1"/>
       <c r="Z238" s="1"/>
@@ -29434,7 +29449,7 @@
       <c r="T239" s="1"/>
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
-      <c r="W239" s="1"/>
+      <c r="W239" s="21"/>
       <c r="X239" s="1"/>
       <c r="Y239" s="1"/>
       <c r="Z239" s="1"/>
@@ -29489,7 +29504,7 @@
       <c r="T240" s="1"/>
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
-      <c r="W240" s="1"/>
+      <c r="W240" s="21"/>
       <c r="X240" s="1"/>
       <c r="Y240" s="1"/>
       <c r="Z240" s="1"/>
@@ -29544,7 +29559,7 @@
       <c r="T241" s="1"/>
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
-      <c r="W241" s="1"/>
+      <c r="W241" s="21"/>
       <c r="X241" s="1"/>
       <c r="Y241" s="1"/>
       <c r="Z241" s="1"/>
@@ -29599,7 +29614,7 @@
       <c r="T242" s="1"/>
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
-      <c r="W242" s="1"/>
+      <c r="W242" s="21"/>
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
       <c r="Z242" s="1"/>
@@ -29654,7 +29669,7 @@
       <c r="T243" s="1"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
-      <c r="W243" s="1"/>
+      <c r="W243" s="21"/>
       <c r="X243" s="1"/>
       <c r="Y243" s="1"/>
       <c r="Z243" s="1"/>
@@ -29709,7 +29724,7 @@
       <c r="T244" s="1"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
-      <c r="W244" s="1"/>
+      <c r="W244" s="21"/>
       <c r="X244" s="1"/>
       <c r="Y244" s="1"/>
       <c r="Z244" s="1"/>
@@ -29764,7 +29779,7 @@
       <c r="T245" s="1"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
-      <c r="W245" s="1"/>
+      <c r="W245" s="21"/>
       <c r="X245" s="1"/>
       <c r="Y245" s="1"/>
       <c r="Z245" s="1"/>
@@ -29819,7 +29834,7 @@
       <c r="T246" s="1"/>
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
-      <c r="W246" s="1"/>
+      <c r="W246" s="21"/>
       <c r="X246" s="1"/>
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
@@ -29874,7 +29889,7 @@
       <c r="T247" s="1"/>
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
-      <c r="W247" s="1"/>
+      <c r="W247" s="21"/>
       <c r="X247" s="1"/>
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
@@ -29929,7 +29944,7 @@
       <c r="T248" s="1"/>
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
-      <c r="W248" s="1"/>
+      <c r="W248" s="21"/>
       <c r="X248" s="1"/>
       <c r="Y248" s="1"/>
       <c r="Z248" s="1"/>
@@ -29984,7 +29999,7 @@
       <c r="T249" s="1"/>
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
-      <c r="W249" s="1"/>
+      <c r="W249" s="21"/>
       <c r="X249" s="1"/>
       <c r="Y249" s="1"/>
       <c r="Z249" s="1"/>
@@ -30039,7 +30054,7 @@
       <c r="T250" s="1"/>
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
-      <c r="W250" s="1"/>
+      <c r="W250" s="21"/>
       <c r="X250" s="1"/>
       <c r="Y250" s="1"/>
       <c r="Z250" s="1"/>
@@ -30094,7 +30109,7 @@
       <c r="T251" s="1"/>
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
-      <c r="W251" s="1"/>
+      <c r="W251" s="21"/>
       <c r="X251" s="1"/>
       <c r="Y251" s="1"/>
       <c r="Z251" s="1"/>
@@ -30149,7 +30164,7 @@
       <c r="T252" s="1"/>
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
-      <c r="W252" s="1"/>
+      <c r="W252" s="21"/>
       <c r="X252" s="1"/>
       <c r="Y252" s="1"/>
       <c r="Z252" s="1"/>
@@ -30204,7 +30219,7 @@
       <c r="T253" s="1"/>
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
-      <c r="W253" s="1"/>
+      <c r="W253" s="21"/>
       <c r="X253" s="1"/>
       <c r="Y253" s="1"/>
       <c r="Z253" s="1"/>
@@ -30259,7 +30274,7 @@
       <c r="T254" s="1"/>
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
-      <c r="W254" s="1"/>
+      <c r="W254" s="21"/>
       <c r="X254" s="1"/>
       <c r="Y254" s="1"/>
       <c r="Z254" s="1"/>
@@ -30314,7 +30329,7 @@
       <c r="T255" s="1"/>
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
-      <c r="W255" s="1"/>
+      <c r="W255" s="21"/>
       <c r="X255" s="1"/>
       <c r="Y255" s="1"/>
       <c r="Z255" s="1"/>
@@ -30369,7 +30384,7 @@
       <c r="T256" s="1"/>
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
-      <c r="W256" s="1"/>
+      <c r="W256" s="21"/>
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
       <c r="Z256" s="1"/>
@@ -30424,7 +30439,7 @@
       <c r="T257" s="1"/>
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
-      <c r="W257" s="1"/>
+      <c r="W257" s="21"/>
       <c r="X257" s="1"/>
       <c r="Y257" s="1"/>
       <c r="Z257" s="1"/>
@@ -30479,7 +30494,7 @@
       <c r="T258" s="1"/>
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
-      <c r="W258" s="1"/>
+      <c r="W258" s="21"/>
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
       <c r="Z258" s="1"/>
@@ -30534,7 +30549,7 @@
       <c r="T259" s="1"/>
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
-      <c r="W259" s="1"/>
+      <c r="W259" s="21"/>
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
       <c r="Z259" s="1"/>
@@ -30589,7 +30604,7 @@
       <c r="T260" s="1"/>
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
-      <c r="W260" s="1"/>
+      <c r="W260" s="21"/>
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
       <c r="Z260" s="1"/>
@@ -30644,7 +30659,7 @@
       <c r="T261" s="1"/>
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
-      <c r="W261" s="1"/>
+      <c r="W261" s="21"/>
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
       <c r="Z261" s="1"/>
@@ -30699,7 +30714,7 @@
       <c r="T262" s="1"/>
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
-      <c r="W262" s="1"/>
+      <c r="W262" s="21"/>
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
       <c r="Z262" s="1"/>
@@ -30754,7 +30769,7 @@
       <c r="T263" s="1"/>
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
-      <c r="W263" s="1"/>
+      <c r="W263" s="21"/>
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
       <c r="Z263" s="1"/>
@@ -30809,7 +30824,7 @@
       <c r="T264" s="1"/>
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
-      <c r="W264" s="1"/>
+      <c r="W264" s="21"/>
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
       <c r="Z264" s="1"/>
@@ -30864,7 +30879,7 @@
       <c r="T265" s="1"/>
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
-      <c r="W265" s="1"/>
+      <c r="W265" s="21"/>
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
       <c r="Z265" s="1"/>
@@ -30919,7 +30934,7 @@
       <c r="T266" s="1"/>
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
-      <c r="W266" s="1"/>
+      <c r="W266" s="21"/>
       <c r="X266" s="1"/>
       <c r="Y266" s="1"/>
       <c r="Z266" s="1"/>
@@ -30974,7 +30989,7 @@
       <c r="T267" s="1"/>
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
-      <c r="W267" s="1"/>
+      <c r="W267" s="21"/>
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
       <c r="Z267" s="1"/>
@@ -31029,7 +31044,7 @@
       <c r="T268" s="1"/>
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
-      <c r="W268" s="1"/>
+      <c r="W268" s="21"/>
       <c r="X268" s="1"/>
       <c r="Y268" s="1"/>
       <c r="Z268" s="1"/>
@@ -31084,7 +31099,7 @@
       <c r="T269" s="1"/>
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
-      <c r="W269" s="1"/>
+      <c r="W269" s="21"/>
       <c r="X269" s="1"/>
       <c r="Y269" s="1"/>
       <c r="Z269" s="1"/>
@@ -31139,7 +31154,7 @@
       <c r="T270" s="1"/>
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
-      <c r="W270" s="1"/>
+      <c r="W270" s="21"/>
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
       <c r="Z270" s="1"/>
@@ -31194,7 +31209,7 @@
       <c r="T271" s="1"/>
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
-      <c r="W271" s="1"/>
+      <c r="W271" s="21"/>
       <c r="X271" s="1"/>
       <c r="Y271" s="1"/>
       <c r="Z271" s="1"/>
@@ -31249,7 +31264,7 @@
       <c r="T272" s="1"/>
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
-      <c r="W272" s="1"/>
+      <c r="W272" s="21"/>
       <c r="X272" s="1"/>
       <c r="Y272" s="1"/>
       <c r="Z272" s="1"/>
@@ -31304,7 +31319,7 @@
       <c r="T273" s="1"/>
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
-      <c r="W273" s="1"/>
+      <c r="W273" s="21"/>
       <c r="X273" s="1"/>
       <c r="Y273" s="1"/>
       <c r="Z273" s="1"/>
@@ -31359,7 +31374,7 @@
       <c r="T274" s="1"/>
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
-      <c r="W274" s="1"/>
+      <c r="W274" s="21"/>
       <c r="X274" s="1"/>
       <c r="Y274" s="1"/>
       <c r="Z274" s="1"/>
@@ -31414,7 +31429,7 @@
       <c r="T275" s="1"/>
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
-      <c r="W275" s="1"/>
+      <c r="W275" s="21"/>
       <c r="X275" s="1"/>
       <c r="Y275" s="1"/>
       <c r="Z275" s="1"/>
@@ -31469,7 +31484,7 @@
       <c r="T276" s="1"/>
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
-      <c r="W276" s="1"/>
+      <c r="W276" s="21"/>
       <c r="X276" s="1"/>
       <c r="Y276" s="1"/>
       <c r="Z276" s="1"/>
@@ -31524,7 +31539,7 @@
       <c r="T277" s="1"/>
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
-      <c r="W277" s="1"/>
+      <c r="W277" s="21"/>
       <c r="X277" s="1"/>
       <c r="Y277" s="1"/>
       <c r="Z277" s="1"/>
@@ -31579,7 +31594,7 @@
       <c r="T278" s="1"/>
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
-      <c r="W278" s="1"/>
+      <c r="W278" s="21"/>
       <c r="X278" s="1"/>
       <c r="Y278" s="1"/>
       <c r="Z278" s="1"/>
@@ -31634,7 +31649,7 @@
       <c r="T279" s="1"/>
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
-      <c r="W279" s="1"/>
+      <c r="W279" s="21"/>
       <c r="X279" s="1"/>
       <c r="Y279" s="1"/>
       <c r="Z279" s="1"/>
@@ -31689,7 +31704,7 @@
       <c r="T280" s="1"/>
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
-      <c r="W280" s="1"/>
+      <c r="W280" s="21"/>
       <c r="X280" s="1"/>
       <c r="Y280" s="1"/>
       <c r="Z280" s="1"/>
@@ -31744,7 +31759,7 @@
       <c r="T281" s="1"/>
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
-      <c r="W281" s="1"/>
+      <c r="W281" s="21"/>
       <c r="X281" s="1"/>
       <c r="Y281" s="1"/>
       <c r="Z281" s="1"/>
@@ -31799,7 +31814,7 @@
       <c r="T282" s="1"/>
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
-      <c r="W282" s="1"/>
+      <c r="W282" s="21"/>
       <c r="X282" s="1"/>
       <c r="Y282" s="1"/>
       <c r="Z282" s="1"/>
@@ -31854,7 +31869,7 @@
       <c r="T283" s="1"/>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
-      <c r="W283" s="1"/>
+      <c r="W283" s="21"/>
       <c r="X283" s="1"/>
       <c r="Y283" s="1"/>
       <c r="Z283" s="1"/>
@@ -31909,7 +31924,7 @@
       <c r="T284" s="1"/>
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
-      <c r="W284" s="1"/>
+      <c r="W284" s="21"/>
       <c r="X284" s="1"/>
       <c r="Y284" s="1"/>
       <c r="Z284" s="1"/>
@@ -31964,7 +31979,7 @@
       <c r="T285" s="1"/>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
-      <c r="W285" s="1"/>
+      <c r="W285" s="21"/>
       <c r="X285" s="1"/>
       <c r="Y285" s="1"/>
       <c r="Z285" s="1"/>
@@ -32019,7 +32034,7 @@
       <c r="T286" s="1"/>
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
-      <c r="W286" s="1"/>
+      <c r="W286" s="21"/>
       <c r="X286" s="1"/>
       <c r="Y286" s="1"/>
       <c r="Z286" s="1"/>
@@ -32074,7 +32089,7 @@
       <c r="T287" s="1"/>
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
-      <c r="W287" s="1"/>
+      <c r="W287" s="21"/>
       <c r="X287" s="1"/>
       <c r="Y287" s="1"/>
       <c r="Z287" s="1"/>
@@ -32129,7 +32144,7 @@
       <c r="T288" s="1"/>
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
-      <c r="W288" s="1"/>
+      <c r="W288" s="21"/>
       <c r="X288" s="1"/>
       <c r="Y288" s="1"/>
       <c r="Z288" s="1"/>
@@ -32184,7 +32199,7 @@
       <c r="T289" s="1"/>
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
-      <c r="W289" s="1"/>
+      <c r="W289" s="21"/>
       <c r="X289" s="1"/>
       <c r="Y289" s="1"/>
       <c r="Z289" s="1"/>
@@ -32239,7 +32254,7 @@
       <c r="T290" s="1"/>
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
-      <c r="W290" s="1"/>
+      <c r="W290" s="21"/>
       <c r="X290" s="1"/>
       <c r="Y290" s="1"/>
       <c r="Z290" s="1"/>
@@ -32294,7 +32309,7 @@
       <c r="T291" s="1"/>
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
-      <c r="W291" s="1"/>
+      <c r="W291" s="21"/>
       <c r="X291" s="1"/>
       <c r="Y291" s="1"/>
       <c r="Z291" s="1"/>
@@ -32349,7 +32364,7 @@
       <c r="T292" s="1"/>
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
-      <c r="W292" s="1"/>
+      <c r="W292" s="21"/>
       <c r="X292" s="1"/>
       <c r="Y292" s="1"/>
       <c r="Z292" s="1"/>
@@ -32404,7 +32419,7 @@
       <c r="T293" s="1"/>
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
-      <c r="W293" s="1"/>
+      <c r="W293" s="21"/>
       <c r="X293" s="1"/>
       <c r="Y293" s="1"/>
       <c r="Z293" s="1"/>
@@ -32459,7 +32474,7 @@
       <c r="T294" s="1"/>
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
-      <c r="W294" s="1"/>
+      <c r="W294" s="21"/>
       <c r="X294" s="1"/>
       <c r="Y294" s="1"/>
       <c r="Z294" s="1"/>
@@ -32514,7 +32529,7 @@
       <c r="T295" s="1"/>
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
-      <c r="W295" s="1"/>
+      <c r="W295" s="21"/>
       <c r="X295" s="1"/>
       <c r="Y295" s="1"/>
       <c r="Z295" s="1"/>
@@ -32569,7 +32584,7 @@
       <c r="T296" s="1"/>
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
-      <c r="W296" s="1"/>
+      <c r="W296" s="21"/>
       <c r="X296" s="1"/>
       <c r="Y296" s="1"/>
       <c r="Z296" s="1"/>
@@ -32624,7 +32639,7 @@
       <c r="T297" s="1"/>
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
-      <c r="W297" s="1"/>
+      <c r="W297" s="21"/>
       <c r="X297" s="1"/>
       <c r="Y297" s="1"/>
       <c r="Z297" s="1"/>
@@ -32679,7 +32694,7 @@
       <c r="T298" s="1"/>
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
-      <c r="W298" s="1"/>
+      <c r="W298" s="21"/>
       <c r="X298" s="1"/>
       <c r="Y298" s="1"/>
       <c r="Z298" s="1"/>
@@ -32734,7 +32749,7 @@
       <c r="T299" s="1"/>
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
-      <c r="W299" s="1"/>
+      <c r="W299" s="21"/>
       <c r="X299" s="1"/>
       <c r="Y299" s="1"/>
       <c r="Z299" s="1"/>
@@ -32789,7 +32804,7 @@
       <c r="T300" s="1"/>
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
-      <c r="W300" s="1"/>
+      <c r="W300" s="21"/>
       <c r="X300" s="1"/>
       <c r="Y300" s="1"/>
       <c r="Z300" s="1"/>
@@ -32844,7 +32859,7 @@
       <c r="T301" s="1"/>
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
-      <c r="W301" s="1"/>
+      <c r="W301" s="21"/>
       <c r="X301" s="1"/>
       <c r="Y301" s="1"/>
       <c r="Z301" s="1"/>
@@ -32899,7 +32914,7 @@
       <c r="T302" s="1"/>
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
-      <c r="W302" s="1"/>
+      <c r="W302" s="21"/>
       <c r="X302" s="1"/>
       <c r="Y302" s="1"/>
       <c r="Z302" s="1"/>
@@ -32954,7 +32969,7 @@
       <c r="T303" s="1"/>
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
-      <c r="W303" s="1"/>
+      <c r="W303" s="21"/>
       <c r="X303" s="1"/>
       <c r="Y303" s="1"/>
       <c r="Z303" s="1"/>
@@ -33009,7 +33024,7 @@
       <c r="T304" s="1"/>
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
-      <c r="W304" s="1"/>
+      <c r="W304" s="21"/>
       <c r="X304" s="1"/>
       <c r="Y304" s="1"/>
       <c r="Z304" s="1"/>
@@ -33064,7 +33079,7 @@
       <c r="T305" s="1"/>
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
-      <c r="W305" s="1"/>
+      <c r="W305" s="21"/>
       <c r="X305" s="1"/>
       <c r="Y305" s="1"/>
       <c r="Z305" s="1"/>
@@ -33119,7 +33134,7 @@
       <c r="T306" s="1"/>
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
-      <c r="W306" s="1"/>
+      <c r="W306" s="21"/>
       <c r="X306" s="1"/>
       <c r="Y306" s="1"/>
       <c r="Z306" s="1"/>
@@ -33174,7 +33189,7 @@
       <c r="T307" s="1"/>
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
-      <c r="W307" s="1"/>
+      <c r="W307" s="21"/>
       <c r="X307" s="1"/>
       <c r="Y307" s="1"/>
       <c r="Z307" s="1"/>
@@ -33229,7 +33244,7 @@
       <c r="T308" s="1"/>
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
-      <c r="W308" s="1"/>
+      <c r="W308" s="21"/>
       <c r="X308" s="1"/>
       <c r="Y308" s="1"/>
       <c r="Z308" s="1"/>
@@ -33284,7 +33299,7 @@
       <c r="T309" s="1"/>
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
-      <c r="W309" s="1"/>
+      <c r="W309" s="21"/>
       <c r="X309" s="1"/>
       <c r="Y309" s="1"/>
       <c r="Z309" s="1"/>
@@ -33339,7 +33354,7 @@
       <c r="T310" s="1"/>
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
-      <c r="W310" s="1"/>
+      <c r="W310" s="21"/>
       <c r="X310" s="1"/>
       <c r="Y310" s="1"/>
       <c r="Z310" s="1"/>
@@ -33394,7 +33409,7 @@
       <c r="T311" s="1"/>
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
-      <c r="W311" s="1"/>
+      <c r="W311" s="21"/>
       <c r="X311" s="1"/>
       <c r="Y311" s="1"/>
       <c r="Z311" s="1"/>
@@ -33449,7 +33464,7 @@
       <c r="T312" s="1"/>
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
-      <c r="W312" s="1"/>
+      <c r="W312" s="21"/>
       <c r="X312" s="1"/>
       <c r="Y312" s="1"/>
       <c r="Z312" s="1"/>
@@ -33504,7 +33519,7 @@
       <c r="T313" s="1"/>
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
-      <c r="W313" s="1"/>
+      <c r="W313" s="21"/>
       <c r="X313" s="1"/>
       <c r="Y313" s="1"/>
       <c r="Z313" s="1"/>
@@ -33559,7 +33574,7 @@
       <c r="T314" s="1"/>
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
-      <c r="W314" s="1"/>
+      <c r="W314" s="21"/>
       <c r="X314" s="1"/>
       <c r="Y314" s="1"/>
       <c r="Z314" s="1"/>
@@ -33614,7 +33629,7 @@
       <c r="T315" s="1"/>
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
-      <c r="W315" s="1"/>
+      <c r="W315" s="21"/>
       <c r="X315" s="1"/>
       <c r="Y315" s="1"/>
       <c r="Z315" s="1"/>
@@ -33669,7 +33684,7 @@
       <c r="T316" s="1"/>
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
-      <c r="W316" s="1"/>
+      <c r="W316" s="21"/>
       <c r="X316" s="1"/>
       <c r="Y316" s="1"/>
       <c r="Z316" s="1"/>
@@ -33724,7 +33739,7 @@
       <c r="T317" s="1"/>
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
-      <c r="W317" s="1"/>
+      <c r="W317" s="21"/>
       <c r="X317" s="1"/>
       <c r="Y317" s="1"/>
       <c r="Z317" s="1"/>
@@ -33779,7 +33794,7 @@
       <c r="T318" s="1"/>
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
-      <c r="W318" s="1"/>
+      <c r="W318" s="21"/>
       <c r="X318" s="1"/>
       <c r="Y318" s="1"/>
       <c r="Z318" s="1"/>
@@ -33834,7 +33849,7 @@
       <c r="T319" s="1"/>
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
-      <c r="W319" s="1"/>
+      <c r="W319" s="21"/>
       <c r="X319" s="1"/>
       <c r="Y319" s="1"/>
       <c r="Z319" s="1"/>
@@ -33889,7 +33904,7 @@
       <c r="T320" s="1"/>
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
-      <c r="W320" s="1"/>
+      <c r="W320" s="21"/>
       <c r="X320" s="1"/>
       <c r="Y320" s="1"/>
       <c r="Z320" s="1"/>
@@ -33944,7 +33959,7 @@
       <c r="T321" s="1"/>
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
-      <c r="W321" s="1"/>
+      <c r="W321" s="21"/>
       <c r="X321" s="1"/>
       <c r="Y321" s="1"/>
       <c r="Z321" s="1"/>
@@ -33999,7 +34014,7 @@
       <c r="T322" s="1"/>
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
-      <c r="W322" s="1"/>
+      <c r="W322" s="21"/>
       <c r="X322" s="1"/>
       <c r="Y322" s="1"/>
       <c r="Z322" s="1"/>
@@ -34054,7 +34069,7 @@
       <c r="T323" s="1"/>
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
-      <c r="W323" s="1"/>
+      <c r="W323" s="21"/>
       <c r="X323" s="1"/>
       <c r="Y323" s="1"/>
       <c r="Z323" s="1"/>
@@ -34109,7 +34124,7 @@
       <c r="T324" s="1"/>
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
-      <c r="W324" s="1"/>
+      <c r="W324" s="21"/>
       <c r="X324" s="1"/>
       <c r="Y324" s="1"/>
       <c r="Z324" s="1"/>
@@ -34164,7 +34179,7 @@
       <c r="T325" s="1"/>
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
-      <c r="W325" s="1"/>
+      <c r="W325" s="21"/>
       <c r="X325" s="1"/>
       <c r="Y325" s="1"/>
       <c r="Z325" s="1"/>
@@ -34219,7 +34234,7 @@
       <c r="T326" s="1"/>
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
-      <c r="W326" s="1"/>
+      <c r="W326" s="21"/>
       <c r="X326" s="1"/>
       <c r="Y326" s="1"/>
       <c r="Z326" s="1"/>
@@ -34274,7 +34289,7 @@
       <c r="T327" s="1"/>
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
-      <c r="W327" s="1"/>
+      <c r="W327" s="21"/>
       <c r="X327" s="1"/>
       <c r="Y327" s="1"/>
       <c r="Z327" s="1"/>
@@ -34329,7 +34344,7 @@
       <c r="T328" s="1"/>
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
-      <c r="W328" s="1"/>
+      <c r="W328" s="21"/>
       <c r="X328" s="1"/>
       <c r="Y328" s="1"/>
       <c r="Z328" s="1"/>
@@ -34384,7 +34399,7 @@
       <c r="T329" s="1"/>
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
-      <c r="W329" s="1"/>
+      <c r="W329" s="21"/>
       <c r="X329" s="1"/>
       <c r="Y329" s="1"/>
       <c r="Z329" s="1"/>
@@ -34439,7 +34454,7 @@
       <c r="T330" s="1"/>
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
-      <c r="W330" s="1"/>
+      <c r="W330" s="21"/>
       <c r="X330" s="1"/>
       <c r="Y330" s="1"/>
       <c r="Z330" s="1"/>
@@ -34494,7 +34509,7 @@
       <c r="T331" s="1"/>
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
-      <c r="W331" s="1"/>
+      <c r="W331" s="21"/>
       <c r="X331" s="1"/>
       <c r="Y331" s="1"/>
       <c r="Z331" s="1"/>
@@ -34549,7 +34564,7 @@
       <c r="T332" s="1"/>
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
-      <c r="W332" s="1"/>
+      <c r="W332" s="21"/>
       <c r="X332" s="1"/>
       <c r="Y332" s="1"/>
       <c r="Z332" s="1"/>
@@ -34604,7 +34619,7 @@
       <c r="T333" s="1"/>
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
-      <c r="W333" s="1"/>
+      <c r="W333" s="21"/>
       <c r="X333" s="1"/>
       <c r="Y333" s="1"/>
       <c r="Z333" s="1"/>
@@ -34659,7 +34674,7 @@
       <c r="T334" s="1"/>
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
-      <c r="W334" s="1"/>
+      <c r="W334" s="21"/>
       <c r="X334" s="1"/>
       <c r="Y334" s="1"/>
       <c r="Z334" s="1"/>
@@ -34714,7 +34729,7 @@
       <c r="T335" s="1"/>
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
-      <c r="W335" s="1"/>
+      <c r="W335" s="21"/>
       <c r="X335" s="1"/>
       <c r="Y335" s="1"/>
       <c r="Z335" s="1"/>
@@ -34769,7 +34784,7 @@
       <c r="T336" s="1"/>
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
-      <c r="W336" s="1"/>
+      <c r="W336" s="21"/>
       <c r="X336" s="1"/>
       <c r="Y336" s="1"/>
       <c r="Z336" s="1"/>
@@ -34824,7 +34839,7 @@
       <c r="T337" s="1"/>
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
-      <c r="W337" s="1"/>
+      <c r="W337" s="21"/>
       <c r="X337" s="1"/>
       <c r="Y337" s="1"/>
       <c r="Z337" s="1"/>
@@ -34879,7 +34894,7 @@
       <c r="T338" s="1"/>
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
-      <c r="W338" s="1"/>
+      <c r="W338" s="21"/>
       <c r="X338" s="1"/>
       <c r="Y338" s="1"/>
       <c r="Z338" s="1"/>
@@ -34934,7 +34949,7 @@
       <c r="T339" s="1"/>
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
-      <c r="W339" s="1"/>
+      <c r="W339" s="21"/>
       <c r="X339" s="1"/>
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
@@ -34989,7 +35004,7 @@
       <c r="T340" s="1"/>
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
-      <c r="W340" s="1"/>
+      <c r="W340" s="21"/>
       <c r="X340" s="1"/>
       <c r="Y340" s="1"/>
       <c r="Z340" s="1"/>
@@ -35044,7 +35059,7 @@
       <c r="T341" s="1"/>
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
-      <c r="W341" s="1"/>
+      <c r="W341" s="21"/>
       <c r="X341" s="1"/>
       <c r="Y341" s="1"/>
       <c r="Z341" s="1"/>
@@ -35099,7 +35114,7 @@
       <c r="T342" s="1"/>
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
-      <c r="W342" s="1"/>
+      <c r="W342" s="21"/>
       <c r="X342" s="1"/>
       <c r="Y342" s="1"/>
       <c r="Z342" s="1"/>
@@ -35154,7 +35169,7 @@
       <c r="T343" s="1"/>
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
-      <c r="W343" s="1"/>
+      <c r="W343" s="21"/>
       <c r="X343" s="1"/>
       <c r="Y343" s="1"/>
       <c r="Z343" s="1"/>
@@ -35209,7 +35224,7 @@
       <c r="T344" s="1"/>
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
-      <c r="W344" s="1"/>
+      <c r="W344" s="21"/>
       <c r="X344" s="1"/>
       <c r="Y344" s="1"/>
       <c r="Z344" s="1"/>
@@ -35264,7 +35279,7 @@
       <c r="T345" s="1"/>
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
-      <c r="W345" s="1"/>
+      <c r="W345" s="21"/>
       <c r="X345" s="1"/>
       <c r="Y345" s="1"/>
       <c r="Z345" s="1"/>
@@ -35319,7 +35334,7 @@
       <c r="T346" s="1"/>
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
-      <c r="W346" s="1"/>
+      <c r="W346" s="21"/>
       <c r="X346" s="1"/>
       <c r="Y346" s="1"/>
       <c r="Z346" s="1"/>
@@ -35374,7 +35389,7 @@
       <c r="T347" s="1"/>
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
-      <c r="W347" s="1"/>
+      <c r="W347" s="21"/>
       <c r="X347" s="1"/>
       <c r="Y347" s="1"/>
       <c r="Z347" s="1"/>
@@ -35429,7 +35444,7 @@
       <c r="T348" s="1"/>
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
-      <c r="W348" s="1"/>
+      <c r="W348" s="21"/>
       <c r="X348" s="1"/>
       <c r="Y348" s="1"/>
       <c r="Z348" s="1"/>
@@ -35484,7 +35499,7 @@
       <c r="T349" s="1"/>
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
-      <c r="W349" s="1"/>
+      <c r="W349" s="21"/>
       <c r="X349" s="1"/>
       <c r="Y349" s="1"/>
       <c r="Z349" s="1"/>
@@ -35539,7 +35554,7 @@
       <c r="T350" s="1"/>
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
-      <c r="W350" s="1"/>
+      <c r="W350" s="21"/>
       <c r="X350" s="1"/>
       <c r="Y350" s="1"/>
       <c r="Z350" s="1"/>
@@ -35594,7 +35609,7 @@
       <c r="T351" s="1"/>
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
-      <c r="W351" s="1"/>
+      <c r="W351" s="21"/>
       <c r="X351" s="1"/>
       <c r="Y351" s="1"/>
       <c r="Z351" s="1"/>
@@ -35649,7 +35664,7 @@
       <c r="T352" s="1"/>
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
-      <c r="W352" s="1"/>
+      <c r="W352" s="21"/>
       <c r="X352" s="1"/>
       <c r="Y352" s="1"/>
       <c r="Z352" s="1"/>
@@ -35704,7 +35719,7 @@
       <c r="T353" s="1"/>
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
-      <c r="W353" s="1"/>
+      <c r="W353" s="21"/>
       <c r="X353" s="1"/>
       <c r="Y353" s="1"/>
       <c r="Z353" s="1"/>
@@ -35759,7 +35774,7 @@
       <c r="T354" s="1"/>
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
-      <c r="W354" s="1"/>
+      <c r="W354" s="21"/>
       <c r="X354" s="1"/>
       <c r="Y354" s="1"/>
       <c r="Z354" s="1"/>
@@ -35814,7 +35829,7 @@
       <c r="T355" s="1"/>
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
-      <c r="W355" s="1"/>
+      <c r="W355" s="21"/>
       <c r="X355" s="1"/>
       <c r="Y355" s="1"/>
       <c r="Z355" s="1"/>
@@ -35869,7 +35884,7 @@
       <c r="T356" s="1"/>
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
-      <c r="W356" s="1"/>
+      <c r="W356" s="21"/>
       <c r="X356" s="1"/>
       <c r="Y356" s="1"/>
       <c r="Z356" s="1"/>
@@ -35924,7 +35939,7 @@
       <c r="T357" s="1"/>
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
-      <c r="W357" s="1"/>
+      <c r="W357" s="21"/>
       <c r="X357" s="1"/>
       <c r="Y357" s="1"/>
       <c r="Z357" s="1"/>
@@ -35979,7 +35994,7 @@
       <c r="T358" s="1"/>
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
-      <c r="W358" s="1"/>
+      <c r="W358" s="21"/>
       <c r="X358" s="1"/>
       <c r="Y358" s="1"/>
       <c r="Z358" s="1"/>
@@ -36034,7 +36049,7 @@
       <c r="T359" s="1"/>
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
-      <c r="W359" s="1"/>
+      <c r="W359" s="21"/>
       <c r="X359" s="1"/>
       <c r="Y359" s="1"/>
       <c r="Z359" s="1"/>
@@ -36089,7 +36104,7 @@
       <c r="T360" s="1"/>
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
-      <c r="W360" s="1"/>
+      <c r="W360" s="21"/>
       <c r="X360" s="1"/>
       <c r="Y360" s="1"/>
       <c r="Z360" s="1"/>
@@ -36144,7 +36159,7 @@
       <c r="T361" s="1"/>
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
-      <c r="W361" s="1"/>
+      <c r="W361" s="21"/>
       <c r="X361" s="1"/>
       <c r="Y361" s="1"/>
       <c r="Z361" s="1"/>
@@ -36199,7 +36214,7 @@
       <c r="T362" s="1"/>
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
-      <c r="W362" s="1"/>
+      <c r="W362" s="21"/>
       <c r="X362" s="1"/>
       <c r="Y362" s="1"/>
       <c r="Z362" s="1"/>
@@ -36254,7 +36269,7 @@
       <c r="T363" s="1"/>
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
-      <c r="W363" s="1"/>
+      <c r="W363" s="21"/>
       <c r="X363" s="1"/>
       <c r="Y363" s="1"/>
       <c r="Z363" s="1"/>
@@ -36309,7 +36324,7 @@
       <c r="T364" s="1"/>
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
-      <c r="W364" s="1"/>
+      <c r="W364" s="21"/>
       <c r="X364" s="1"/>
       <c r="Y364" s="1"/>
       <c r="Z364" s="1"/>
@@ -36364,7 +36379,7 @@
       <c r="T365" s="1"/>
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
-      <c r="W365" s="1"/>
+      <c r="W365" s="21"/>
       <c r="X365" s="1"/>
       <c r="Y365" s="1"/>
       <c r="Z365" s="1"/>
@@ -36419,7 +36434,7 @@
       <c r="T366" s="1"/>
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
-      <c r="W366" s="1"/>
+      <c r="W366" s="21"/>
       <c r="X366" s="1"/>
       <c r="Y366" s="1"/>
       <c r="Z366" s="1"/>
@@ -36474,7 +36489,7 @@
       <c r="T367" s="1"/>
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
-      <c r="W367" s="1"/>
+      <c r="W367" s="21"/>
       <c r="X367" s="1"/>
       <c r="Y367" s="1"/>
       <c r="Z367" s="1"/>
@@ -36529,7 +36544,7 @@
       <c r="T368" s="1"/>
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
-      <c r="W368" s="1"/>
+      <c r="W368" s="21"/>
       <c r="X368" s="1"/>
       <c r="Y368" s="1"/>
       <c r="Z368" s="1"/>
@@ -36584,7 +36599,7 @@
       <c r="T369" s="1"/>
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
-      <c r="W369" s="1"/>
+      <c r="W369" s="21"/>
       <c r="X369" s="1"/>
       <c r="Y369" s="1"/>
       <c r="Z369" s="1"/>
@@ -36639,7 +36654,7 @@
       <c r="T370" s="1"/>
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
-      <c r="W370" s="1"/>
+      <c r="W370" s="21"/>
       <c r="X370" s="1"/>
       <c r="Y370" s="1"/>
       <c r="Z370" s="1"/>
@@ -36694,7 +36709,7 @@
       <c r="T371" s="1"/>
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
-      <c r="W371" s="1"/>
+      <c r="W371" s="21"/>
       <c r="X371" s="1"/>
       <c r="Y371" s="1"/>
       <c r="Z371" s="1"/>
@@ -36749,7 +36764,7 @@
       <c r="T372" s="1"/>
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
-      <c r="W372" s="1"/>
+      <c r="W372" s="21"/>
       <c r="X372" s="1"/>
       <c r="Y372" s="1"/>
       <c r="Z372" s="1"/>
@@ -36804,7 +36819,7 @@
       <c r="T373" s="1"/>
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
-      <c r="W373" s="1"/>
+      <c r="W373" s="21"/>
       <c r="X373" s="1"/>
       <c r="Y373" s="1"/>
       <c r="Z373" s="1"/>
@@ -36859,7 +36874,7 @@
       <c r="T374" s="1"/>
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
-      <c r="W374" s="1"/>
+      <c r="W374" s="21"/>
       <c r="X374" s="1"/>
       <c r="Y374" s="1"/>
       <c r="Z374" s="1"/>
@@ -36914,7 +36929,7 @@
       <c r="T375" s="1"/>
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
-      <c r="W375" s="1"/>
+      <c r="W375" s="21"/>
       <c r="X375" s="1"/>
       <c r="Y375" s="1"/>
       <c r="Z375" s="1"/>
@@ -36969,7 +36984,7 @@
       <c r="T376" s="1"/>
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
-      <c r="W376" s="1"/>
+      <c r="W376" s="21"/>
       <c r="X376" s="1"/>
       <c r="Y376" s="1"/>
       <c r="Z376" s="1"/>
@@ -37024,7 +37039,7 @@
       <c r="T377" s="1"/>
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
-      <c r="W377" s="1"/>
+      <c r="W377" s="21"/>
       <c r="X377" s="1"/>
       <c r="Y377" s="1"/>
       <c r="Z377" s="1"/>
@@ -37079,7 +37094,7 @@
       <c r="T378" s="1"/>
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
-      <c r="W378" s="1"/>
+      <c r="W378" s="21"/>
       <c r="X378" s="1"/>
       <c r="Y378" s="1"/>
       <c r="Z378" s="1"/>
@@ -37134,7 +37149,7 @@
       <c r="T379" s="1"/>
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
-      <c r="W379" s="1"/>
+      <c r="W379" s="21"/>
       <c r="X379" s="1"/>
       <c r="Y379" s="1"/>
       <c r="Z379" s="1"/>
@@ -37189,7 +37204,7 @@
       <c r="T380" s="1"/>
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
-      <c r="W380" s="1"/>
+      <c r="W380" s="21"/>
       <c r="X380" s="1"/>
       <c r="Y380" s="1"/>
       <c r="Z380" s="1"/>
@@ -37244,7 +37259,7 @@
       <c r="T381" s="1"/>
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
-      <c r="W381" s="1"/>
+      <c r="W381" s="21"/>
       <c r="X381" s="1"/>
       <c r="Y381" s="1"/>
       <c r="Z381" s="1"/>
@@ -37299,7 +37314,7 @@
       <c r="T382" s="1"/>
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
-      <c r="W382" s="1"/>
+      <c r="W382" s="21"/>
       <c r="X382" s="1"/>
       <c r="Y382" s="1"/>
       <c r="Z382" s="1"/>
@@ -37354,7 +37369,7 @@
       <c r="T383" s="1"/>
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
-      <c r="W383" s="1"/>
+      <c r="W383" s="21"/>
       <c r="X383" s="1"/>
       <c r="Y383" s="1"/>
       <c r="Z383" s="1"/>
@@ -37409,7 +37424,7 @@
       <c r="T384" s="1"/>
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
-      <c r="W384" s="1"/>
+      <c r="W384" s="21"/>
       <c r="X384" s="1"/>
       <c r="Y384" s="1"/>
       <c r="Z384" s="1"/>
@@ -37464,7 +37479,7 @@
       <c r="T385" s="1"/>
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
-      <c r="W385" s="1"/>
+      <c r="W385" s="21"/>
       <c r="X385" s="1"/>
       <c r="Y385" s="1"/>
       <c r="Z385" s="1"/>
@@ -37519,7 +37534,7 @@
       <c r="T386" s="1"/>
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
-      <c r="W386" s="1"/>
+      <c r="W386" s="21"/>
       <c r="X386" s="1"/>
       <c r="Y386" s="1"/>
       <c r="Z386" s="1"/>
@@ -37574,7 +37589,7 @@
       <c r="T387" s="1"/>
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
-      <c r="W387" s="1"/>
+      <c r="W387" s="21"/>
       <c r="X387" s="1"/>
       <c r="Y387" s="1"/>
       <c r="Z387" s="1"/>
@@ -37629,7 +37644,7 @@
       <c r="T388" s="1"/>
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
-      <c r="W388" s="1"/>
+      <c r="W388" s="21"/>
       <c r="X388" s="1"/>
       <c r="Y388" s="1"/>
       <c r="Z388" s="1"/>
@@ -37684,7 +37699,7 @@
       <c r="T389" s="1"/>
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
-      <c r="W389" s="1"/>
+      <c r="W389" s="21"/>
       <c r="X389" s="1"/>
       <c r="Y389" s="1"/>
       <c r="Z389" s="1"/>
@@ -37739,7 +37754,7 @@
       <c r="T390" s="1"/>
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
-      <c r="W390" s="1"/>
+      <c r="W390" s="21"/>
       <c r="X390" s="1"/>
       <c r="Y390" s="1"/>
       <c r="Z390" s="1"/>
@@ -37794,7 +37809,7 @@
       <c r="T391" s="1"/>
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
-      <c r="W391" s="1"/>
+      <c r="W391" s="21"/>
       <c r="X391" s="1"/>
       <c r="Y391" s="1"/>
       <c r="Z391" s="1"/>
@@ -37849,7 +37864,7 @@
       <c r="T392" s="1"/>
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
-      <c r="W392" s="1"/>
+      <c r="W392" s="21"/>
       <c r="X392" s="1"/>
       <c r="Y392" s="1"/>
       <c r="Z392" s="1"/>
@@ -37904,7 +37919,7 @@
       <c r="T393" s="1"/>
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
-      <c r="W393" s="1"/>
+      <c r="W393" s="21"/>
       <c r="X393" s="1"/>
       <c r="Y393" s="1"/>
       <c r="Z393" s="1"/>
@@ -37959,7 +37974,7 @@
       <c r="T394" s="1"/>
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
-      <c r="W394" s="1"/>
+      <c r="W394" s="21"/>
       <c r="X394" s="1"/>
       <c r="Y394" s="1"/>
       <c r="Z394" s="1"/>
@@ -38014,7 +38029,7 @@
       <c r="T395" s="1"/>
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
-      <c r="W395" s="1"/>
+      <c r="W395" s="21"/>
       <c r="X395" s="1"/>
       <c r="Y395" s="1"/>
       <c r="Z395" s="1"/>
@@ -38069,7 +38084,7 @@
       <c r="T396" s="1"/>
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
-      <c r="W396" s="1"/>
+      <c r="W396" s="21"/>
       <c r="X396" s="1"/>
       <c r="Y396" s="1"/>
       <c r="Z396" s="1"/>
@@ -38124,7 +38139,7 @@
       <c r="T397" s="1"/>
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
-      <c r="W397" s="1"/>
+      <c r="W397" s="21"/>
       <c r="X397" s="1"/>
       <c r="Y397" s="1"/>
       <c r="Z397" s="1"/>
@@ -38179,7 +38194,7 @@
       <c r="T398" s="1"/>
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
-      <c r="W398" s="1"/>
+      <c r="W398" s="21"/>
       <c r="X398" s="1"/>
       <c r="Y398" s="1"/>
       <c r="Z398" s="1"/>
@@ -38234,7 +38249,7 @@
       <c r="T399" s="1"/>
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
-      <c r="W399" s="1"/>
+      <c r="W399" s="21"/>
       <c r="X399" s="1"/>
       <c r="Y399" s="1"/>
       <c r="Z399" s="1"/>
@@ -38289,7 +38304,7 @@
       <c r="T400" s="1"/>
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
-      <c r="W400" s="1"/>
+      <c r="W400" s="21"/>
       <c r="X400" s="1"/>
       <c r="Y400" s="1"/>
       <c r="Z400" s="1"/>
@@ -38344,7 +38359,7 @@
       <c r="T401" s="1"/>
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
-      <c r="W401" s="1"/>
+      <c r="W401" s="21"/>
       <c r="X401" s="1"/>
       <c r="Y401" s="1"/>
       <c r="Z401" s="1"/>
@@ -38399,7 +38414,7 @@
       <c r="T402" s="1"/>
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
-      <c r="W402" s="1"/>
+      <c r="W402" s="21"/>
       <c r="X402" s="1"/>
       <c r="Y402" s="1"/>
       <c r="Z402" s="1"/>
@@ -38454,7 +38469,7 @@
       <c r="T403" s="1"/>
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
-      <c r="W403" s="1"/>
+      <c r="W403" s="21"/>
       <c r="X403" s="1"/>
       <c r="Y403" s="1"/>
       <c r="Z403" s="1"/>
@@ -38509,7 +38524,7 @@
       <c r="T404" s="1"/>
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
-      <c r="W404" s="1"/>
+      <c r="W404" s="21"/>
       <c r="X404" s="1"/>
       <c r="Y404" s="1"/>
       <c r="Z404" s="1"/>
@@ -38564,7 +38579,7 @@
       <c r="T405" s="1"/>
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
-      <c r="W405" s="1"/>
+      <c r="W405" s="21"/>
       <c r="X405" s="1"/>
       <c r="Y405" s="1"/>
       <c r="Z405" s="1"/>
@@ -38619,7 +38634,7 @@
       <c r="T406" s="1"/>
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
-      <c r="W406" s="1"/>
+      <c r="W406" s="21"/>
       <c r="X406" s="1"/>
       <c r="Y406" s="1"/>
       <c r="Z406" s="1"/>
@@ -38674,7 +38689,7 @@
       <c r="T407" s="1"/>
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
-      <c r="W407" s="1"/>
+      <c r="W407" s="21"/>
       <c r="X407" s="1"/>
       <c r="Y407" s="1"/>
       <c r="Z407" s="1"/>
@@ -38729,7 +38744,7 @@
       <c r="T408" s="1"/>
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
-      <c r="W408" s="1"/>
+      <c r="W408" s="21"/>
       <c r="X408" s="1"/>
       <c r="Y408" s="1"/>
       <c r="Z408" s="1"/>
@@ -38784,7 +38799,7 @@
       <c r="T409" s="1"/>
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
-      <c r="W409" s="1"/>
+      <c r="W409" s="21"/>
       <c r="X409" s="1"/>
       <c r="Y409" s="1"/>
       <c r="Z409" s="1"/>
@@ -38839,7 +38854,7 @@
       <c r="T410" s="1"/>
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
-      <c r="W410" s="1"/>
+      <c r="W410" s="21"/>
       <c r="X410" s="1"/>
       <c r="Y410" s="1"/>
       <c r="Z410" s="1"/>
@@ -38894,7 +38909,7 @@
       <c r="T411" s="1"/>
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
-      <c r="W411" s="1"/>
+      <c r="W411" s="21"/>
       <c r="X411" s="1"/>
       <c r="Y411" s="1"/>
       <c r="Z411" s="1"/>
@@ -38949,7 +38964,7 @@
       <c r="T412" s="1"/>
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
-      <c r="W412" s="1"/>
+      <c r="W412" s="21"/>
       <c r="X412" s="1"/>
       <c r="Y412" s="1"/>
       <c r="Z412" s="1"/>
@@ -39004,7 +39019,7 @@
       <c r="T413" s="1"/>
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
-      <c r="W413" s="1"/>
+      <c r="W413" s="21"/>
       <c r="X413" s="1"/>
       <c r="Y413" s="1"/>
       <c r="Z413" s="1"/>
@@ -39059,7 +39074,7 @@
       <c r="T414" s="1"/>
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
-      <c r="W414" s="1"/>
+      <c r="W414" s="21"/>
       <c r="X414" s="1"/>
       <c r="Y414" s="1"/>
       <c r="Z414" s="1"/>
@@ -39114,7 +39129,7 @@
       <c r="T415" s="1"/>
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
-      <c r="W415" s="1"/>
+      <c r="W415" s="21"/>
       <c r="X415" s="1"/>
       <c r="Y415" s="1"/>
       <c r="Z415" s="1"/>
@@ -39169,7 +39184,7 @@
       <c r="T416" s="1"/>
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
-      <c r="W416" s="1"/>
+      <c r="W416" s="21"/>
       <c r="X416" s="1"/>
       <c r="Y416" s="1"/>
       <c r="Z416" s="1"/>
@@ -39224,7 +39239,7 @@
       <c r="T417" s="1"/>
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
-      <c r="W417" s="1"/>
+      <c r="W417" s="21"/>
       <c r="X417" s="1"/>
       <c r="Y417" s="1"/>
       <c r="Z417" s="1"/>
@@ -39279,7 +39294,7 @@
       <c r="T418" s="1"/>
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
-      <c r="W418" s="1"/>
+      <c r="W418" s="21"/>
       <c r="X418" s="1"/>
       <c r="Y418" s="1"/>
       <c r="Z418" s="1"/>
@@ -39334,7 +39349,7 @@
       <c r="T419" s="1"/>
       <c r="U419" s="1"/>
       <c r="V419" s="1"/>
-      <c r="W419" s="1"/>
+      <c r="W419" s="21"/>
       <c r="X419" s="1"/>
       <c r="Y419" s="1"/>
       <c r="Z419" s="1"/>
@@ -39389,7 +39404,7 @@
       <c r="T420" s="1"/>
       <c r="U420" s="1"/>
       <c r="V420" s="1"/>
-      <c r="W420" s="1"/>
+      <c r="W420" s="21"/>
       <c r="X420" s="1"/>
       <c r="Y420" s="1"/>
       <c r="Z420" s="1"/>
@@ -39444,7 +39459,7 @@
       <c r="T421" s="1"/>
       <c r="U421" s="1"/>
       <c r="V421" s="1"/>
-      <c r="W421" s="1"/>
+      <c r="W421" s="21"/>
       <c r="X421" s="1"/>
       <c r="Y421" s="1"/>
       <c r="Z421" s="1"/>
@@ -39499,7 +39514,7 @@
       <c r="T422" s="1"/>
       <c r="U422" s="1"/>
       <c r="V422" s="1"/>
-      <c r="W422" s="1"/>
+      <c r="W422" s="21"/>
       <c r="X422" s="1"/>
       <c r="Y422" s="1"/>
       <c r="Z422" s="1"/>
@@ -39554,7 +39569,7 @@
       <c r="T423" s="1"/>
       <c r="U423" s="1"/>
       <c r="V423" s="1"/>
-      <c r="W423" s="1"/>
+      <c r="W423" s="21"/>
       <c r="X423" s="1"/>
       <c r="Y423" s="1"/>
       <c r="Z423" s="1"/>
@@ -39609,7 +39624,7 @@
       <c r="T424" s="1"/>
       <c r="U424" s="1"/>
       <c r="V424" s="1"/>
-      <c r="W424" s="1"/>
+      <c r="W424" s="21"/>
       <c r="X424" s="1"/>
       <c r="Y424" s="1"/>
       <c r="Z424" s="1"/>
@@ -39664,7 +39679,7 @@
       <c r="T425" s="1"/>
       <c r="U425" s="1"/>
       <c r="V425" s="1"/>
-      <c r="W425" s="1"/>
+      <c r="W425" s="21"/>
       <c r="X425" s="1"/>
       <c r="Y425" s="1"/>
       <c r="Z425" s="1"/>
@@ -39719,7 +39734,7 @@
       <c r="T426" s="1"/>
       <c r="U426" s="1"/>
       <c r="V426" s="1"/>
-      <c r="W426" s="1"/>
+      <c r="W426" s="21"/>
       <c r="X426" s="1"/>
       <c r="Y426" s="1"/>
       <c r="Z426" s="1"/>
@@ -39774,7 +39789,7 @@
       <c r="T427" s="1"/>
       <c r="U427" s="1"/>
       <c r="V427" s="1"/>
-      <c r="W427" s="1"/>
+      <c r="W427" s="21"/>
       <c r="X427" s="1"/>
       <c r="Y427" s="1"/>
       <c r="Z427" s="1"/>
@@ -39829,7 +39844,7 @@
       <c r="T428" s="1"/>
       <c r="U428" s="1"/>
       <c r="V428" s="1"/>
-      <c r="W428" s="1"/>
+      <c r="W428" s="21"/>
       <c r="X428" s="1"/>
       <c r="Y428" s="1"/>
       <c r="Z428" s="1"/>
@@ -39884,7 +39899,7 @@
       <c r="T429" s="1"/>
       <c r="U429" s="1"/>
       <c r="V429" s="1"/>
-      <c r="W429" s="1"/>
+      <c r="W429" s="21"/>
       <c r="X429" s="1"/>
       <c r="Y429" s="1"/>
       <c r="Z429" s="1"/>
@@ -39939,7 +39954,7 @@
       <c r="T430" s="1"/>
       <c r="U430" s="1"/>
       <c r="V430" s="1"/>
-      <c r="W430" s="1"/>
+      <c r="W430" s="21"/>
       <c r="X430" s="1"/>
       <c r="Y430" s="1"/>
       <c r="Z430" s="1"/>
@@ -39994,7 +40009,7 @@
       <c r="T431" s="1"/>
       <c r="U431" s="1"/>
       <c r="V431" s="1"/>
-      <c r="W431" s="1"/>
+      <c r="W431" s="21"/>
       <c r="X431" s="1"/>
       <c r="Y431" s="1"/>
       <c r="Z431" s="1"/>
@@ -40049,7 +40064,7 @@
       <c r="T432" s="1"/>
       <c r="U432" s="1"/>
       <c r="V432" s="1"/>
-      <c r="W432" s="1"/>
+      <c r="W432" s="21"/>
       <c r="X432" s="1"/>
       <c r="Y432" s="1"/>
       <c r="Z432" s="1"/>
@@ -40104,7 +40119,7 @@
       <c r="T433" s="1"/>
       <c r="U433" s="1"/>
       <c r="V433" s="1"/>
-      <c r="W433" s="1"/>
+      <c r="W433" s="21"/>
       <c r="X433" s="1"/>
       <c r="Y433" s="1"/>
       <c r="Z433" s="1"/>
@@ -40159,7 +40174,7 @@
       <c r="T434" s="1"/>
       <c r="U434" s="1"/>
       <c r="V434" s="1"/>
-      <c r="W434" s="1"/>
+      <c r="W434" s="21"/>
       <c r="X434" s="1"/>
       <c r="Y434" s="1"/>
       <c r="Z434" s="1"/>
@@ -40214,7 +40229,7 @@
       <c r="T435" s="1"/>
       <c r="U435" s="1"/>
       <c r="V435" s="1"/>
-      <c r="W435" s="1"/>
+      <c r="W435" s="21"/>
       <c r="X435" s="1"/>
       <c r="Y435" s="1"/>
       <c r="Z435" s="1"/>
@@ -40269,7 +40284,7 @@
       <c r="T436" s="1"/>
       <c r="U436" s="1"/>
       <c r="V436" s="1"/>
-      <c r="W436" s="1"/>
+      <c r="W436" s="21"/>
       <c r="X436" s="1"/>
       <c r="Y436" s="1"/>
       <c r="Z436" s="1"/>
@@ -40324,7 +40339,7 @@
       <c r="T437" s="1"/>
       <c r="U437" s="1"/>
       <c r="V437" s="1"/>
-      <c r="W437" s="1"/>
+      <c r="W437" s="21"/>
       <c r="X437" s="1"/>
       <c r="Y437" s="1"/>
       <c r="Z437" s="1"/>
@@ -40379,7 +40394,7 @@
       <c r="T438" s="1"/>
       <c r="U438" s="1"/>
       <c r="V438" s="1"/>
-      <c r="W438" s="1"/>
+      <c r="W438" s="21"/>
       <c r="X438" s="1"/>
       <c r="Y438" s="1"/>
       <c r="Z438" s="1"/>
@@ -40434,7 +40449,7 @@
       <c r="T439" s="1"/>
       <c r="U439" s="1"/>
       <c r="V439" s="1"/>
-      <c r="W439" s="1"/>
+      <c r="W439" s="21"/>
       <c r="X439" s="1"/>
       <c r="Y439" s="1"/>
       <c r="Z439" s="1"/>
@@ -40489,7 +40504,7 @@
       <c r="T440" s="1"/>
       <c r="U440" s="1"/>
       <c r="V440" s="1"/>
-      <c r="W440" s="1"/>
+      <c r="W440" s="21"/>
       <c r="X440" s="1"/>
       <c r="Y440" s="1"/>
       <c r="Z440" s="1"/>
@@ -40544,7 +40559,7 @@
       <c r="T441" s="1"/>
       <c r="U441" s="1"/>
       <c r="V441" s="1"/>
-      <c r="W441" s="1"/>
+      <c r="W441" s="21"/>
       <c r="X441" s="1"/>
       <c r="Y441" s="1"/>
       <c r="Z441" s="1"/>
@@ -40599,7 +40614,7 @@
       <c r="T442" s="1"/>
       <c r="U442" s="1"/>
       <c r="V442" s="1"/>
-      <c r="W442" s="1"/>
+      <c r="W442" s="21"/>
       <c r="X442" s="1"/>
       <c r="Y442" s="1"/>
       <c r="Z442" s="1"/>
@@ -40654,7 +40669,7 @@
       <c r="T443" s="1"/>
       <c r="U443" s="1"/>
       <c r="V443" s="1"/>
-      <c r="W443" s="1"/>
+      <c r="W443" s="21"/>
       <c r="X443" s="1"/>
       <c r="Y443" s="1"/>
       <c r="Z443" s="1"/>
@@ -40709,7 +40724,7 @@
       <c r="T444" s="1"/>
       <c r="U444" s="1"/>
       <c r="V444" s="1"/>
-      <c r="W444" s="1"/>
+      <c r="W444" s="21"/>
       <c r="X444" s="1"/>
       <c r="Y444" s="1"/>
       <c r="Z444" s="1"/>
@@ -40764,7 +40779,7 @@
       <c r="T445" s="1"/>
       <c r="U445" s="1"/>
       <c r="V445" s="1"/>
-      <c r="W445" s="1"/>
+      <c r="W445" s="21"/>
       <c r="X445" s="1"/>
       <c r="Y445" s="1"/>
       <c r="Z445" s="1"/>
@@ -40819,7 +40834,7 @@
       <c r="T446" s="1"/>
       <c r="U446" s="1"/>
       <c r="V446" s="1"/>
-      <c r="W446" s="1"/>
+      <c r="W446" s="21"/>
       <c r="X446" s="1"/>
       <c r="Y446" s="1"/>
       <c r="Z446" s="1"/>
@@ -40874,7 +40889,7 @@
       <c r="T447" s="1"/>
       <c r="U447" s="1"/>
       <c r="V447" s="1"/>
-      <c r="W447" s="1"/>
+      <c r="W447" s="21"/>
       <c r="X447" s="1"/>
       <c r="Y447" s="1"/>
       <c r="Z447" s="1"/>
@@ -40929,7 +40944,7 @@
       <c r="T448" s="1"/>
       <c r="U448" s="1"/>
       <c r="V448" s="1"/>
-      <c r="W448" s="1"/>
+      <c r="W448" s="21"/>
       <c r="X448" s="1"/>
       <c r="Y448" s="1"/>
       <c r="Z448" s="1"/>
@@ -40984,7 +40999,7 @@
       <c r="T449" s="1"/>
       <c r="U449" s="1"/>
       <c r="V449" s="1"/>
-      <c r="W449" s="1"/>
+      <c r="W449" s="21"/>
       <c r="X449" s="1"/>
       <c r="Y449" s="1"/>
       <c r="Z449" s="1"/>
@@ -41039,7 +41054,7 @@
       <c r="T450" s="1"/>
       <c r="U450" s="1"/>
       <c r="V450" s="1"/>
-      <c r="W450" s="1"/>
+      <c r="W450" s="21"/>
       <c r="X450" s="1"/>
       <c r="Y450" s="1"/>
       <c r="Z450" s="1"/>
@@ -41094,7 +41109,7 @@
       <c r="T451" s="1"/>
       <c r="U451" s="1"/>
       <c r="V451" s="1"/>
-      <c r="W451" s="1"/>
+      <c r="W451" s="21"/>
       <c r="X451" s="1"/>
       <c r="Y451" s="1"/>
       <c r="Z451" s="1"/>
@@ -41149,7 +41164,7 @@
       <c r="T452" s="1"/>
       <c r="U452" s="1"/>
       <c r="V452" s="1"/>
-      <c r="W452" s="1"/>
+      <c r="W452" s="21"/>
       <c r="X452" s="1"/>
       <c r="Y452" s="1"/>
       <c r="Z452" s="1"/>
@@ -41204,7 +41219,7 @@
       <c r="T453" s="1"/>
       <c r="U453" s="1"/>
       <c r="V453" s="1"/>
-      <c r="W453" s="1"/>
+      <c r="W453" s="21"/>
       <c r="X453" s="1"/>
       <c r="Y453" s="1"/>
       <c r="Z453" s="1"/>
@@ -41259,7 +41274,7 @@
       <c r="T454" s="1"/>
       <c r="U454" s="1"/>
       <c r="V454" s="1"/>
-      <c r="W454" s="1"/>
+      <c r="W454" s="21"/>
       <c r="X454" s="1"/>
       <c r="Y454" s="1"/>
       <c r="Z454" s="1"/>
@@ -41314,7 +41329,7 @@
       <c r="T455" s="1"/>
       <c r="U455" s="1"/>
       <c r="V455" s="1"/>
-      <c r="W455" s="1"/>
+      <c r="W455" s="21"/>
       <c r="X455" s="1"/>
       <c r="Y455" s="1"/>
       <c r="Z455" s="1"/>
@@ -41369,7 +41384,7 @@
       <c r="T456" s="1"/>
       <c r="U456" s="1"/>
       <c r="V456" s="1"/>
-      <c r="W456" s="1"/>
+      <c r="W456" s="21"/>
       <c r="X456" s="1"/>
       <c r="Y456" s="1"/>
       <c r="Z456" s="1"/>
@@ -41424,7 +41439,7 @@
       <c r="T457" s="1"/>
       <c r="U457" s="1"/>
       <c r="V457" s="1"/>
-      <c r="W457" s="1"/>
+      <c r="W457" s="21"/>
       <c r="X457" s="1"/>
       <c r="Y457" s="1"/>
       <c r="Z457" s="1"/>
@@ -41479,7 +41494,7 @@
       <c r="T458" s="1"/>
       <c r="U458" s="1"/>
       <c r="V458" s="1"/>
-      <c r="W458" s="1"/>
+      <c r="W458" s="21"/>
       <c r="X458" s="1"/>
       <c r="Y458" s="1"/>
       <c r="Z458" s="1"/>
@@ -41534,7 +41549,7 @@
       <c r="T459" s="1"/>
       <c r="U459" s="1"/>
       <c r="V459" s="1"/>
-      <c r="W459" s="1"/>
+      <c r="W459" s="21"/>
       <c r="X459" s="1"/>
       <c r="Y459" s="1"/>
       <c r="Z459" s="1"/>
@@ -41589,7 +41604,7 @@
       <c r="T460" s="1"/>
       <c r="U460" s="1"/>
       <c r="V460" s="1"/>
-      <c r="W460" s="1"/>
+      <c r="W460" s="21"/>
       <c r="X460" s="1"/>
       <c r="Y460" s="1"/>
       <c r="Z460" s="1"/>
@@ -41644,7 +41659,7 @@
       <c r="T461" s="1"/>
       <c r="U461" s="1"/>
       <c r="V461" s="1"/>
-      <c r="W461" s="1"/>
+      <c r="W461" s="21"/>
       <c r="X461" s="1"/>
       <c r="Y461" s="1"/>
       <c r="Z461" s="1"/>
@@ -41699,7 +41714,7 @@
       <c r="T462" s="1"/>
       <c r="U462" s="1"/>
       <c r="V462" s="1"/>
-      <c r="W462" s="1"/>
+      <c r="W462" s="21"/>
       <c r="X462" s="1"/>
       <c r="Y462" s="1"/>
       <c r="Z462" s="1"/>
@@ -41754,7 +41769,7 @@
       <c r="T463" s="1"/>
       <c r="U463" s="1"/>
       <c r="V463" s="1"/>
-      <c r="W463" s="1"/>
+      <c r="W463" s="21"/>
       <c r="X463" s="1"/>
       <c r="Y463" s="1"/>
       <c r="Z463" s="1"/>
@@ -41809,7 +41824,7 @@
       <c r="T464" s="1"/>
       <c r="U464" s="1"/>
       <c r="V464" s="1"/>
-      <c r="W464" s="1"/>
+      <c r="W464" s="21"/>
       <c r="X464" s="1"/>
       <c r="Y464" s="1"/>
       <c r="Z464" s="1"/>
@@ -41864,7 +41879,7 @@
       <c r="T465" s="1"/>
       <c r="U465" s="1"/>
       <c r="V465" s="1"/>
-      <c r="W465" s="1"/>
+      <c r="W465" s="21"/>
       <c r="X465" s="1"/>
       <c r="Y465" s="1"/>
       <c r="Z465" s="1"/>
@@ -41919,7 +41934,7 @@
       <c r="T466" s="1"/>
       <c r="U466" s="1"/>
       <c r="V466" s="1"/>
-      <c r="W466" s="1"/>
+      <c r="W466" s="21"/>
       <c r="X466" s="1"/>
       <c r="Y466" s="1"/>
       <c r="Z466" s="1"/>
@@ -41974,7 +41989,7 @@
       <c r="T467" s="1"/>
       <c r="U467" s="1"/>
       <c r="V467" s="1"/>
-      <c r="W467" s="1"/>
+      <c r="W467" s="21"/>
       <c r="X467" s="1"/>
       <c r="Y467" s="1"/>
       <c r="Z467" s="1"/>
@@ -42029,7 +42044,7 @@
       <c r="T468" s="1"/>
       <c r="U468" s="1"/>
       <c r="V468" s="1"/>
-      <c r="W468" s="1"/>
+      <c r="W468" s="21"/>
       <c r="X468" s="1"/>
       <c r="Y468" s="1"/>
       <c r="Z468" s="1"/>
@@ -42084,7 +42099,7 @@
       <c r="T469" s="1"/>
       <c r="U469" s="1"/>
       <c r="V469" s="1"/>
-      <c r="W469" s="1"/>
+      <c r="W469" s="21"/>
       <c r="X469" s="1"/>
       <c r="Y469" s="1"/>
       <c r="Z469" s="1"/>
@@ -42139,7 +42154,7 @@
       <c r="T470" s="1"/>
       <c r="U470" s="1"/>
       <c r="V470" s="1"/>
-      <c r="W470" s="1"/>
+      <c r="W470" s="21"/>
       <c r="X470" s="1"/>
       <c r="Y470" s="1"/>
       <c r="Z470" s="1"/>
@@ -42194,7 +42209,7 @@
       <c r="T471" s="1"/>
       <c r="U471" s="1"/>
       <c r="V471" s="1"/>
-      <c r="W471" s="1"/>
+      <c r="W471" s="21"/>
       <c r="X471" s="1"/>
       <c r="Y471" s="1"/>
       <c r="Z471" s="1"/>
@@ -42249,7 +42264,7 @@
       <c r="T472" s="1"/>
       <c r="U472" s="1"/>
       <c r="V472" s="1"/>
-      <c r="W472" s="1"/>
+      <c r="W472" s="21"/>
       <c r="X472" s="1"/>
       <c r="Y472" s="1"/>
       <c r="Z472" s="1"/>
@@ -42304,7 +42319,7 @@
       <c r="T473" s="1"/>
       <c r="U473" s="1"/>
       <c r="V473" s="1"/>
-      <c r="W473" s="1"/>
+      <c r="W473" s="21"/>
       <c r="X473" s="1"/>
       <c r="Y473" s="1"/>
       <c r="Z473" s="1"/>
@@ -42359,7 +42374,7 @@
       <c r="T474" s="1"/>
       <c r="U474" s="1"/>
       <c r="V474" s="1"/>
-      <c r="W474" s="1"/>
+      <c r="W474" s="21"/>
       <c r="X474" s="1"/>
       <c r="Y474" s="1"/>
       <c r="Z474" s="1"/>
@@ -42414,7 +42429,7 @@
       <c r="T475" s="1"/>
       <c r="U475" s="1"/>
       <c r="V475" s="1"/>
-      <c r="W475" s="1"/>
+      <c r="W475" s="21"/>
       <c r="X475" s="1"/>
       <c r="Y475" s="1"/>
       <c r="Z475" s="1"/>
@@ -42469,7 +42484,7 @@
       <c r="T476" s="1"/>
       <c r="U476" s="1"/>
       <c r="V476" s="1"/>
-      <c r="W476" s="1"/>
+      <c r="W476" s="21"/>
       <c r="X476" s="1"/>
       <c r="Y476" s="1"/>
       <c r="Z476" s="1"/>
@@ -42524,7 +42539,7 @@
       <c r="T477" s="1"/>
       <c r="U477" s="1"/>
       <c r="V477" s="1"/>
-      <c r="W477" s="1"/>
+      <c r="W477" s="21"/>
       <c r="X477" s="1"/>
       <c r="Y477" s="1"/>
       <c r="Z477" s="1"/>
@@ -42579,7 +42594,7 @@
       <c r="T478" s="1"/>
       <c r="U478" s="1"/>
       <c r="V478" s="1"/>
-      <c r="W478" s="1"/>
+      <c r="W478" s="21"/>
       <c r="X478" s="1"/>
       <c r="Y478" s="1"/>
       <c r="Z478" s="1"/>
@@ -42634,7 +42649,7 @@
       <c r="T479" s="1"/>
       <c r="U479" s="1"/>
       <c r="V479" s="1"/>
-      <c r="W479" s="1"/>
+      <c r="W479" s="21"/>
       <c r="X479" s="1"/>
       <c r="Y479" s="1"/>
       <c r="Z479" s="1"/>
@@ -42689,7 +42704,7 @@
       <c r="T480" s="1"/>
       <c r="U480" s="1"/>
       <c r="V480" s="1"/>
-      <c r="W480" s="1"/>
+      <c r="W480" s="21"/>
       <c r="X480" s="1"/>
       <c r="Y480" s="1"/>
       <c r="Z480" s="1"/>
@@ -42744,7 +42759,7 @@
       <c r="T481" s="1"/>
       <c r="U481" s="1"/>
       <c r="V481" s="1"/>
-      <c r="W481" s="1"/>
+      <c r="W481" s="21"/>
       <c r="X481" s="1"/>
       <c r="Y481" s="1"/>
       <c r="Z481" s="1"/>
@@ -42799,7 +42814,7 @@
       <c r="T482" s="1"/>
       <c r="U482" s="1"/>
       <c r="V482" s="1"/>
-      <c r="W482" s="1"/>
+      <c r="W482" s="21"/>
       <c r="X482" s="1"/>
       <c r="Y482" s="1"/>
       <c r="Z482" s="1"/>
@@ -42854,7 +42869,7 @@
       <c r="T483" s="1"/>
       <c r="U483" s="1"/>
       <c r="V483" s="1"/>
-      <c r="W483" s="1"/>
+      <c r="W483" s="21"/>
       <c r="X483" s="1"/>
       <c r="Y483" s="1"/>
       <c r="Z483" s="1"/>
@@ -42909,7 +42924,7 @@
       <c r="T484" s="1"/>
       <c r="U484" s="1"/>
       <c r="V484" s="1"/>
-      <c r="W484" s="1"/>
+      <c r="W484" s="21"/>
       <c r="X484" s="1"/>
       <c r="Y484" s="1"/>
       <c r="Z484" s="1"/>
@@ -42964,7 +42979,7 @@
       <c r="T485" s="1"/>
       <c r="U485" s="1"/>
       <c r="V485" s="1"/>
-      <c r="W485" s="1"/>
+      <c r="W485" s="21"/>
       <c r="X485" s="1"/>
       <c r="Y485" s="1"/>
       <c r="Z485" s="1"/>
@@ -43019,7 +43034,7 @@
       <c r="T486" s="1"/>
       <c r="U486" s="1"/>
       <c r="V486" s="1"/>
-      <c r="W486" s="1"/>
+      <c r="W486" s="21"/>
       <c r="X486" s="1"/>
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
@@ -43074,7 +43089,7 @@
       <c r="T487" s="1"/>
       <c r="U487" s="1"/>
       <c r="V487" s="1"/>
-      <c r="W487" s="1"/>
+      <c r="W487" s="21"/>
       <c r="X487" s="1"/>
       <c r="Y487" s="1"/>
       <c r="Z487" s="1"/>
@@ -43129,7 +43144,7 @@
       <c r="T488" s="1"/>
       <c r="U488" s="1"/>
       <c r="V488" s="1"/>
-      <c r="W488" s="1"/>
+      <c r="W488" s="21"/>
       <c r="X488" s="1"/>
       <c r="Y488" s="1"/>
       <c r="Z488" s="1"/>
@@ -43184,7 +43199,7 @@
       <c r="T489" s="1"/>
       <c r="U489" s="1"/>
       <c r="V489" s="1"/>
-      <c r="W489" s="1"/>
+      <c r="W489" s="21"/>
       <c r="X489" s="1"/>
       <c r="Y489" s="1"/>
       <c r="Z489" s="1"/>
@@ -43239,7 +43254,7 @@
       <c r="T490" s="1"/>
       <c r="U490" s="1"/>
       <c r="V490" s="1"/>
-      <c r="W490" s="1"/>
+      <c r="W490" s="21"/>
       <c r="X490" s="1"/>
       <c r="Y490" s="1"/>
       <c r="Z490" s="1"/>
@@ -43294,7 +43309,7 @@
       <c r="T491" s="1"/>
       <c r="U491" s="1"/>
       <c r="V491" s="1"/>
-      <c r="W491" s="1"/>
+      <c r="W491" s="21"/>
       <c r="X491" s="1"/>
       <c r="Y491" s="1"/>
       <c r="Z491" s="1"/>
@@ -43349,7 +43364,7 @@
       <c r="T492" s="1"/>
       <c r="U492" s="1"/>
       <c r="V492" s="1"/>
-      <c r="W492" s="1"/>
+      <c r="W492" s="21"/>
       <c r="X492" s="1"/>
       <c r="Y492" s="1"/>
       <c r="Z492" s="1"/>
@@ -43404,7 +43419,7 @@
       <c r="T493" s="1"/>
       <c r="U493" s="1"/>
       <c r="V493" s="1"/>
-      <c r="W493" s="1"/>
+      <c r="W493" s="21"/>
       <c r="X493" s="1"/>
       <c r="Y493" s="1"/>
       <c r="Z493" s="1"/>
@@ -43459,7 +43474,7 @@
       <c r="T494" s="1"/>
       <c r="U494" s="1"/>
       <c r="V494" s="1"/>
-      <c r="W494" s="1"/>
+      <c r="W494" s="21"/>
       <c r="X494" s="1"/>
       <c r="Y494" s="1"/>
       <c r="Z494" s="1"/>
@@ -43514,7 +43529,7 @@
       <c r="T495" s="1"/>
       <c r="U495" s="1"/>
       <c r="V495" s="1"/>
-      <c r="W495" s="1"/>
+      <c r="W495" s="21"/>
       <c r="X495" s="1"/>
       <c r="Y495" s="1"/>
       <c r="Z495" s="1"/>
@@ -43569,7 +43584,7 @@
       <c r="T496" s="1"/>
       <c r="U496" s="1"/>
       <c r="V496" s="1"/>
-      <c r="W496" s="1"/>
+      <c r="W496" s="21"/>
       <c r="X496" s="1"/>
       <c r="Y496" s="1"/>
       <c r="Z496" s="1"/>
@@ -43624,7 +43639,7 @@
       <c r="T497" s="1"/>
       <c r="U497" s="1"/>
       <c r="V497" s="1"/>
-      <c r="W497" s="1"/>
+      <c r="W497" s="21"/>
       <c r="X497" s="1"/>
       <c r="Y497" s="1"/>
       <c r="Z497" s="1"/>
@@ -43679,7 +43694,7 @@
       <c r="T498" s="1"/>
       <c r="U498" s="1"/>
       <c r="V498" s="1"/>
-      <c r="W498" s="1"/>
+      <c r="W498" s="21"/>
       <c r="X498" s="1"/>
       <c r="Y498" s="1"/>
       <c r="Z498" s="1"/>
@@ -43734,7 +43749,7 @@
       <c r="T499" s="1"/>
       <c r="U499" s="1"/>
       <c r="V499" s="1"/>
-      <c r="W499" s="1"/>
+      <c r="W499" s="21"/>
       <c r="X499" s="1"/>
       <c r="Y499" s="1"/>
       <c r="Z499" s="1"/>
@@ -43789,7 +43804,7 @@
       <c r="T500" s="1"/>
       <c r="U500" s="1"/>
       <c r="V500" s="1"/>
-      <c r="W500" s="1"/>
+      <c r="W500" s="21"/>
       <c r="X500" s="1"/>
       <c r="Y500" s="1"/>
       <c r="Z500" s="1"/>
